--- a/data/qc_raw_data.xlsx
+++ b/data/qc_raw_data.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IsmailGargouri\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IsmailGargouri\Downloads\qc_score_public_site\public_dashboard_site\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{934BF4EA-181C-4844-9024-F472F4554F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FD353F-D4B4-4DF5-837E-49D2A92EEC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED9107AD-9FAA-41DC-95E8-BD114CE9C0F8}"/>
   </bookViews>
   <sheets>
     <sheet name="QC Raw Data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'QC Raw Data'!$A$1:$EL$319</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -4161,6 +4164,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BD147F-8F6E-45B5-9A89-00EAC144C500}">
   <dimension ref="A1:EL319"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="33" max="33" width="25.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:142" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -91498,6 +91504,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:EL319" xr:uid="{A5BD147F-8F6E-45B5-9A89-00EAC144C500}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/qc_raw_data.xlsx
+++ b/data/qc_raw_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IsmailGargouri\Downloads\qc_score_public_site\public_dashboard_site\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3FB7AE3-538A-4EF7-9E0C-3DA8080F30B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55EA532B-2373-4E26-8CB5-2CE29B80F6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{CE841D12-FF01-43C6-A7E8-40DCCEE635D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{995AE9A5-AF6B-40F1-B565-838826E9BB48}"/>
   </bookViews>
   <sheets>
     <sheet name="QC Raw Data" sheetId="1" r:id="rId1"/>
@@ -4350,7 +4350,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D66CFEA1-C10F-4FE6-B5F9-73906CC7AB90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102D79A2-0EF0-4EFD-BE2D-D7A25700DD46}">
   <dimension ref="A1:EL360"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/data/qc_raw_data.xlsx
+++ b/data/qc_raw_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blackgoldfarms-my.sharepoint.com/personal/ismail_gargouri_blackgoldfarms_com/Documents/Desktop/qc_score_public_site/public_dashboard_site/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{C4C23450-0DD7-4502-81AB-84EC1B5D5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC9F07CB-30B9-482F-8043-798DE5DA29FF}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{C4C23450-0DD7-4502-81AB-84EC1B5D5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50E34028-6EDC-4204-BD92-A0EC486CB974}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{825DA881-BA9E-41EF-B82A-180C9DE360E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{825DA881-BA9E-41EF-B82A-180C9DE360E7}"/>
   </bookViews>
   <sheets>
     <sheet name="QC Raw Data" sheetId="1" r:id="rId1"/>
@@ -2713,6 +2713,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3032,6 +3036,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F50CD2-FD3B-47DB-AA7D-C7DA447965F7}">
   <dimension ref="A1:EL205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:142" x14ac:dyDescent="0.25">
       <c r="A1" t="s">

--- a/data/qc_raw_data.xlsx
+++ b/data/qc_raw_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blackgoldfarms-my.sharepoint.com/personal/ismail_gargouri_blackgoldfarms_com/Documents/Desktop/qc_score_public_site/public_dashboard_site/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{C4C23450-0DD7-4502-81AB-84EC1B5D5652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50E34028-6EDC-4204-BD92-A0EC486CB974}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9080F06A-D724-47B3-859C-CD69B96471AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{825DA881-BA9E-41EF-B82A-180C9DE360E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E265B2B4-7793-4710-B7C1-F58E4F8CFAB4}"/>
   </bookViews>
   <sheets>
     <sheet name="QC Raw Data" sheetId="1" r:id="rId1"/>
@@ -1048,1126 +1048,1126 @@
     <t>0006267238</t>
   </si>
   <si>
+    <t>012000</t>
+  </si>
+  <si>
+    <t>4507454607-00090-0006267239</t>
+  </si>
+  <si>
+    <t>0006267239</t>
+  </si>
+  <si>
+    <t>065600</t>
+  </si>
+  <si>
+    <t>4507454607-00100-0006267240</t>
+  </si>
+  <si>
+    <t>0006267240</t>
+  </si>
+  <si>
+    <t>4507459814-00010-0006268079</t>
+  </si>
+  <si>
+    <t>0006268079</t>
+  </si>
+  <si>
+    <t>043000</t>
+  </si>
+  <si>
+    <t>064100</t>
+  </si>
+  <si>
+    <t>4507459814-00020-0006268080</t>
+  </si>
+  <si>
+    <t>0006268080</t>
+  </si>
+  <si>
+    <t>4507459814-00030-0006268081</t>
+  </si>
+  <si>
+    <t>0006268081</t>
+  </si>
+  <si>
+    <t>032500</t>
+  </si>
+  <si>
+    <t>082100</t>
+  </si>
+  <si>
+    <t>4507459814-00040-0006268082</t>
+  </si>
+  <si>
+    <t>0006268082</t>
+  </si>
+  <si>
+    <t>062800</t>
+  </si>
+  <si>
+    <t>4507459814-00050-0006268083</t>
+  </si>
+  <si>
+    <t>0006268083</t>
+  </si>
+  <si>
+    <t>093300</t>
+  </si>
+  <si>
+    <t>4507459814-00060-0006268084</t>
+  </si>
+  <si>
+    <t>0006268084</t>
+  </si>
+  <si>
+    <t>022500</t>
+  </si>
+  <si>
+    <t>4507459814-00070-0006268085</t>
+  </si>
+  <si>
+    <t>0006268085</t>
+  </si>
+  <si>
+    <t>4507459814-00080-0006268086</t>
+  </si>
+  <si>
+    <t>0006268086</t>
+  </si>
+  <si>
+    <t>063700</t>
+  </si>
+  <si>
+    <t>4507459814-00090-0006268087</t>
+  </si>
+  <si>
+    <t>0006268087</t>
+  </si>
+  <si>
+    <t>092600</t>
+  </si>
+  <si>
+    <t>040900</t>
+  </si>
+  <si>
+    <t>4507459814-00100-0006268088</t>
+  </si>
+  <si>
+    <t>0006268088</t>
+  </si>
+  <si>
+    <t>LYNCHBURG</t>
+  </si>
+  <si>
+    <t>4507509204-00010-0006277080</t>
+  </si>
+  <si>
+    <t>0006277080</t>
+  </si>
+  <si>
+    <t>083000</t>
+  </si>
+  <si>
+    <t>4507509204-00020-0006277081</t>
+  </si>
+  <si>
+    <t>0006277081</t>
+  </si>
+  <si>
+    <t>4507523441-00050-0006279699</t>
+  </si>
+  <si>
+    <t>0006279699</t>
+  </si>
+  <si>
+    <t>043900</t>
+  </si>
+  <si>
+    <t>4507523441-00060-0006279700</t>
+  </si>
+  <si>
+    <t>0006279700</t>
+  </si>
+  <si>
+    <t>4507523940-00010-0006279776</t>
+  </si>
+  <si>
+    <t>0006279776</t>
+  </si>
+  <si>
+    <t>4507524031-00010-0006279815</t>
+  </si>
+  <si>
+    <t>0006279815</t>
+  </si>
+  <si>
+    <t>4507410004-00030-0006221876</t>
+  </si>
+  <si>
+    <t>0006221876</t>
+  </si>
+  <si>
+    <t>050900</t>
+  </si>
+  <si>
+    <t>4507410004-00050-0006221878</t>
+  </si>
+  <si>
+    <t>0006221878</t>
+  </si>
+  <si>
+    <t>072000</t>
+  </si>
+  <si>
+    <t>4507410004-00070-0006221880</t>
+  </si>
+  <si>
+    <t>0006221880</t>
+  </si>
+  <si>
+    <t>020500</t>
+  </si>
+  <si>
+    <t>4507410004-00080-0006221881</t>
+  </si>
+  <si>
+    <t>0006221881</t>
+  </si>
+  <si>
+    <t>4507410004-00090-0006221882</t>
+  </si>
+  <si>
+    <t>0006221882</t>
+  </si>
+  <si>
+    <t>4507489629-00010-0006272473</t>
+  </si>
+  <si>
+    <t>0006272473</t>
+  </si>
+  <si>
+    <t>024900</t>
+  </si>
+  <si>
+    <t>4507489629-00020-0006272474</t>
+  </si>
+  <si>
+    <t>0006272474</t>
+  </si>
+  <si>
+    <t>074200</t>
+  </si>
+  <si>
+    <t>095500</t>
+  </si>
+  <si>
+    <t>4507489629-00030-0006272475</t>
+  </si>
+  <si>
+    <t>0006272475</t>
+  </si>
+  <si>
+    <t>4507489629-00040-0006272476</t>
+  </si>
+  <si>
+    <t>0006272476</t>
+  </si>
+  <si>
+    <t>4507505041-00010-0006275972</t>
+  </si>
+  <si>
+    <t>0006275972</t>
+  </si>
+  <si>
+    <t>091400</t>
+  </si>
+  <si>
+    <t>4507523441-00010-0006279695</t>
+  </si>
+  <si>
+    <t>0006279695</t>
+  </si>
+  <si>
+    <t>014500</t>
+  </si>
+  <si>
+    <t>4507523441-00020-0006279696</t>
+  </si>
+  <si>
+    <t>0006279696</t>
+  </si>
+  <si>
+    <t>4507523441-00030-0006279697</t>
+  </si>
+  <si>
+    <t>0006279697</t>
+  </si>
+  <si>
+    <t>003000</t>
+  </si>
+  <si>
+    <t>4507523441-00040-0006279698</t>
+  </si>
+  <si>
+    <t>0006279698</t>
+  </si>
+  <si>
+    <t>021300</t>
+  </si>
+  <si>
+    <t>PERRY</t>
+  </si>
+  <si>
+    <t>4507408907-00100-0006219770</t>
+  </si>
+  <si>
+    <t>0006219770</t>
+  </si>
+  <si>
+    <t>083500</t>
+  </si>
+  <si>
+    <t>4507408907-00110-0006219771</t>
+  </si>
+  <si>
+    <t>0006219771</t>
+  </si>
+  <si>
+    <t>4507408907-00120-0006219772</t>
+  </si>
+  <si>
+    <t>0006219772</t>
+  </si>
+  <si>
+    <t>4507408907-00130-0006219773</t>
+  </si>
+  <si>
+    <t>0006219773</t>
+  </si>
+  <si>
+    <t>4507408907-00140-0006219774</t>
+  </si>
+  <si>
+    <t>0006219774</t>
+  </si>
+  <si>
+    <t>4507408907-00150-0006219775</t>
+  </si>
+  <si>
+    <t>0006219775</t>
+  </si>
+  <si>
+    <t>4507408907-00160-0006219776</t>
+  </si>
+  <si>
+    <t>0006219776</t>
+  </si>
+  <si>
+    <t>4507408907-00170-0006219777</t>
+  </si>
+  <si>
+    <t>0006219777</t>
+  </si>
+  <si>
+    <t>4507408907-00180-0006219778</t>
+  </si>
+  <si>
+    <t>0006219778</t>
+  </si>
+  <si>
+    <t>4507408907-00190-0006219779</t>
+  </si>
+  <si>
+    <t>0006219779</t>
+  </si>
+  <si>
+    <t>4507487488-00010-0006271943</t>
+  </si>
+  <si>
+    <t>0006271943</t>
+  </si>
+  <si>
+    <t>SUPER PUFF</t>
+  </si>
+  <si>
+    <t>4507425196-00060-0006258828</t>
+  </si>
+  <si>
+    <t>0006258828</t>
+  </si>
+  <si>
+    <t>4507425196-00070-0006258829</t>
+  </si>
+  <si>
+    <t>0006258829</t>
+  </si>
+  <si>
+    <t>000001</t>
+  </si>
+  <si>
+    <t>4507425196-00080-0006258830</t>
+  </si>
+  <si>
+    <t>0006258830</t>
+  </si>
+  <si>
+    <t>052000</t>
+  </si>
+  <si>
+    <t>4507425196-00090-0006258831</t>
+  </si>
+  <si>
+    <t>0006258831</t>
+  </si>
+  <si>
+    <t>4507425196-00100-0006258832</t>
+  </si>
+  <si>
+    <t>0006258832</t>
+  </si>
+  <si>
+    <t>4507425196-00110-0006258833</t>
+  </si>
+  <si>
+    <t>0006258833</t>
+  </si>
+  <si>
+    <t>4507425196-00120-0006258834</t>
+  </si>
+  <si>
+    <t>0006258834</t>
+  </si>
+  <si>
+    <t>4507425196-00040-0006258826</t>
+  </si>
+  <si>
+    <t>0006258826</t>
+  </si>
+  <si>
+    <t>021700</t>
+  </si>
+  <si>
+    <t>083216</t>
+  </si>
+  <si>
+    <t>4507425196-00050-0006258827</t>
+  </si>
+  <si>
+    <t>0006258827</t>
+  </si>
+  <si>
+    <t>4507488019-00010-0006272103</t>
+  </si>
+  <si>
+    <t>0006272103</t>
+  </si>
+  <si>
+    <t>4507488019-00020-0006272104</t>
+  </si>
+  <si>
+    <t>0006272104</t>
+  </si>
+  <si>
+    <t>010702</t>
+  </si>
+  <si>
+    <t>4507488019-00030-0006272105</t>
+  </si>
+  <si>
+    <t>0006272105</t>
+  </si>
+  <si>
+    <t>4507491884-00010-0006272987</t>
+  </si>
+  <si>
+    <t>0006272987</t>
+  </si>
+  <si>
+    <t>060243</t>
+  </si>
+  <si>
+    <t>4507508326-00010-0006276419</t>
+  </si>
+  <si>
+    <t>0006276419</t>
+  </si>
+  <si>
+    <t>WATERFORD</t>
+  </si>
+  <si>
+    <t>4507425051-00110-0006258793</t>
+  </si>
+  <si>
+    <t>0006258793</t>
+  </si>
+  <si>
+    <t>4507425051-00120-0006258794</t>
+  </si>
+  <si>
+    <t>0006258794</t>
+  </si>
+  <si>
+    <t>4507425051-00130-0006258795</t>
+  </si>
+  <si>
+    <t>0006258795</t>
+  </si>
+  <si>
+    <t>4507425051-00140-0006258796</t>
+  </si>
+  <si>
+    <t>0006258796</t>
+  </si>
+  <si>
+    <t>4507425051-00150-0006258797</t>
+  </si>
+  <si>
+    <t>0006258797</t>
+  </si>
+  <si>
+    <t>4507425051-00160-0006258798</t>
+  </si>
+  <si>
+    <t>0006258798</t>
+  </si>
+  <si>
+    <t>4507425051-00170-0006258799</t>
+  </si>
+  <si>
+    <t>0006258799</t>
+  </si>
+  <si>
+    <t>4507425051-00180-0006258800</t>
+  </si>
+  <si>
+    <t>0006258800</t>
+  </si>
+  <si>
+    <t>4507425051-00190-0006258801</t>
+  </si>
+  <si>
+    <t>0006258801</t>
+  </si>
+  <si>
+    <t>4507425051-00200-0006258802</t>
+  </si>
+  <si>
+    <t>0006258802</t>
+  </si>
+  <si>
+    <t>4507425051-00210-0006258803</t>
+  </si>
+  <si>
+    <t>0006258803</t>
+  </si>
+  <si>
+    <t>4507425051-00220-0006258804</t>
+  </si>
+  <si>
+    <t>0006258804</t>
+  </si>
+  <si>
+    <t>4507425051-00230-0006258805</t>
+  </si>
+  <si>
+    <t>0006258805</t>
+  </si>
+  <si>
+    <t>00230</t>
+  </si>
+  <si>
+    <t>4507425051-00240-0006258806</t>
+  </si>
+  <si>
+    <t>0006258806</t>
+  </si>
+  <si>
+    <t>00240</t>
+  </si>
+  <si>
+    <t>4507425051-00250-0006258807</t>
+  </si>
+  <si>
+    <t>0006258807</t>
+  </si>
+  <si>
+    <t>4507439331-00160-0006262814</t>
+  </si>
+  <si>
+    <t>0006262814</t>
+  </si>
+  <si>
+    <t>4507439331-00170-0006262815</t>
+  </si>
+  <si>
+    <t>0006262815</t>
+  </si>
+  <si>
+    <t>4507439331-00180-0006262816</t>
+  </si>
+  <si>
+    <t>0006262816</t>
+  </si>
+  <si>
+    <t>4507439331-00190-0006262817</t>
+  </si>
+  <si>
+    <t>0006262817</t>
+  </si>
+  <si>
+    <t>4507439331-00200-0006262818</t>
+  </si>
+  <si>
+    <t>0006262818</t>
+  </si>
+  <si>
+    <t>4507439331-00210-0006262819</t>
+  </si>
+  <si>
+    <t>0006262819</t>
+  </si>
+  <si>
+    <t>4507439331-00220-0006262820</t>
+  </si>
+  <si>
+    <t>0006262820</t>
+  </si>
+  <si>
+    <t>MIS-BLACK GOLD FARMS</t>
+  </si>
+  <si>
+    <t>074600</t>
+  </si>
+  <si>
+    <t>074644</t>
+  </si>
+  <si>
+    <t>4507439331-00230-0006262821</t>
+  </si>
+  <si>
+    <t>0006262821</t>
+  </si>
+  <si>
+    <t>4507439331-00240-0006262822</t>
+  </si>
+  <si>
+    <t>0006262822</t>
+  </si>
+  <si>
+    <t>4507493285-00010-0006273349</t>
+  </si>
+  <si>
+    <t>0006273349</t>
+  </si>
+  <si>
+    <t>4507493285-00020-0006273350</t>
+  </si>
+  <si>
+    <t>0006273350</t>
+  </si>
+  <si>
+    <t>4507493285-00030-0006273351</t>
+  </si>
+  <si>
+    <t>0006273351</t>
+  </si>
+  <si>
+    <t>4507439331-00110-0006262809</t>
+  </si>
+  <si>
+    <t>0006262809</t>
+  </si>
+  <si>
+    <t>INW-BLACK GOLD FARMS IN 0885</t>
+  </si>
+  <si>
+    <t>4507439331-00120-0006262810</t>
+  </si>
+  <si>
+    <t>0006262810</t>
+  </si>
+  <si>
+    <t>4507439331-00130-0006262811</t>
+  </si>
+  <si>
+    <t>0006262811</t>
+  </si>
+  <si>
+    <t>4507439331-00140-0006262812</t>
+  </si>
+  <si>
+    <t>0006262812</t>
+  </si>
+  <si>
+    <t>4507439331-00150-0006262813</t>
+  </si>
+  <si>
+    <t>0006262813</t>
+  </si>
+  <si>
+    <t>INW-BLACK GOLD FARMS</t>
+  </si>
+  <si>
+    <t>4507439331-00250-0006262823</t>
+  </si>
+  <si>
+    <t>0006262823</t>
+  </si>
+  <si>
+    <t>4507493285-00040-0006273352</t>
+  </si>
+  <si>
+    <t>0006273352</t>
+  </si>
+  <si>
+    <t>WOOSTER</t>
+  </si>
+  <si>
+    <t>4507508738-00010-0006276601</t>
+  </si>
+  <si>
+    <t>0006276601</t>
+  </si>
+  <si>
+    <t>4507508738-00020-0006276602</t>
+  </si>
+  <si>
+    <t>0006276602</t>
+  </si>
+  <si>
+    <t>4507508738-00030-0006276603</t>
+  </si>
+  <si>
+    <t>0006276603</t>
+  </si>
+  <si>
+    <t>4507508738-00040-0006276604</t>
+  </si>
+  <si>
+    <t>0006276604</t>
+  </si>
+  <si>
+    <t>4507508738-00050-0006276605</t>
+  </si>
+  <si>
+    <t>0006276605</t>
+  </si>
+  <si>
+    <t>4507508738-00060-0006276606</t>
+  </si>
+  <si>
+    <t>0006276606</t>
+  </si>
+  <si>
+    <t>4507508738-00070-0006276607</t>
+  </si>
+  <si>
+    <t>0006276607</t>
+  </si>
+  <si>
+    <t>4507508738-00080-0006276608</t>
+  </si>
+  <si>
+    <t>0006276608</t>
+  </si>
+  <si>
+    <t>4507508738-00090-0006276609</t>
+  </si>
+  <si>
+    <t>0006276609</t>
+  </si>
+  <si>
+    <t>4507508738-00100-0006276610</t>
+  </si>
+  <si>
+    <t>0006276610</t>
+  </si>
+  <si>
+    <t>4507508738-00110-0006276611</t>
+  </si>
+  <si>
+    <t>0006276611</t>
+  </si>
+  <si>
+    <t>4507471133-00010-0006269152</t>
+  </si>
+  <si>
+    <t>0006269152</t>
+  </si>
+  <si>
+    <t>063000</t>
+  </si>
+  <si>
+    <t>YORK</t>
+  </si>
+  <si>
+    <t>4507420978-00170-0006256771</t>
+  </si>
+  <si>
+    <t>0006256771</t>
+  </si>
+  <si>
+    <t>093000</t>
+  </si>
+  <si>
+    <t>095900</t>
+  </si>
+  <si>
+    <t>4507420978-00210-0006256775</t>
+  </si>
+  <si>
+    <t>0006256775</t>
+  </si>
+  <si>
+    <t>4507420978-00220-0006256776</t>
+  </si>
+  <si>
+    <t>0006256776</t>
+  </si>
+  <si>
+    <t>015400</t>
+  </si>
+  <si>
+    <t>4507420978-00230-0006256777</t>
+  </si>
+  <si>
+    <t>0006256777</t>
+  </si>
+  <si>
+    <t>040800</t>
+  </si>
+  <si>
+    <t>4507420978-00250-0006256779</t>
+  </si>
+  <si>
+    <t>0006256779</t>
+  </si>
+  <si>
+    <t>4507420978-00290-0006256783</t>
+  </si>
+  <si>
+    <t>0006256783</t>
+  </si>
+  <si>
+    <t>00290</t>
+  </si>
+  <si>
+    <t>4507420978-00310-0006256785</t>
+  </si>
+  <si>
+    <t>0006256785</t>
+  </si>
+  <si>
+    <t>00310</t>
+  </si>
+  <si>
+    <t>4507420978-00320-0006256786</t>
+  </si>
+  <si>
+    <t>0006256786</t>
+  </si>
+  <si>
+    <t>00320</t>
+  </si>
+  <si>
+    <t>4507420978-00330-0006256787</t>
+  </si>
+  <si>
+    <t>0006256787</t>
+  </si>
+  <si>
+    <t>00330</t>
+  </si>
+  <si>
+    <t>4507420978-00040-0006256758</t>
+  </si>
+  <si>
+    <t>0006256758</t>
+  </si>
+  <si>
+    <t>033400</t>
+  </si>
+  <si>
+    <t>4507420978-00050-0006256759</t>
+  </si>
+  <si>
+    <t>0006256759</t>
+  </si>
+  <si>
+    <t>054700</t>
+  </si>
+  <si>
+    <t>4507420978-00060-0006256760</t>
+  </si>
+  <si>
+    <t>0006256760</t>
+  </si>
+  <si>
+    <t>073200</t>
+  </si>
+  <si>
+    <t>4507420978-00070-0006256761</t>
+  </si>
+  <si>
+    <t>0006256761</t>
+  </si>
+  <si>
+    <t>092900</t>
+  </si>
+  <si>
+    <t>4507420978-00080-0006256762</t>
+  </si>
+  <si>
+    <t>0006256762</t>
+  </si>
+  <si>
+    <t>4507420978-00090-0006256763</t>
+  </si>
+  <si>
+    <t>0006256763</t>
+  </si>
+  <si>
+    <t>4507420978-00100-0006256764</t>
+  </si>
+  <si>
+    <t>0006256764</t>
+  </si>
+  <si>
+    <t>4507420978-00110-0006256765</t>
+  </si>
+  <si>
+    <t>0006256765</t>
+  </si>
+  <si>
+    <t>4507420978-00120-0006256766</t>
+  </si>
+  <si>
+    <t>0006256766</t>
+  </si>
+  <si>
+    <t>4507420978-00130-0006256767</t>
+  </si>
+  <si>
+    <t>0006256767</t>
+  </si>
+  <si>
+    <t>4507420978-00140-0006256768</t>
+  </si>
+  <si>
+    <t>0006256768</t>
+  </si>
+  <si>
+    <t>060400</t>
+  </si>
+  <si>
+    <t>4507420978-00150-0006256769</t>
+  </si>
+  <si>
+    <t>0006256769</t>
+  </si>
+  <si>
+    <t>023800</t>
+  </si>
+  <si>
+    <t>081100</t>
+  </si>
+  <si>
+    <t>4507420978-00160-0006256770</t>
+  </si>
+  <si>
+    <t>0006256770</t>
+  </si>
+  <si>
+    <t>052300</t>
+  </si>
+  <si>
+    <t>4507420978-00180-0006256772</t>
+  </si>
+  <si>
+    <t>0006256772</t>
+  </si>
+  <si>
+    <t>4507420978-00190-0006256773</t>
+  </si>
+  <si>
+    <t>0006256773</t>
+  </si>
+  <si>
+    <t>4507420978-00200-0006256774</t>
+  </si>
+  <si>
+    <t>0006256774</t>
+  </si>
+  <si>
+    <t>4507420978-00240-0006256778</t>
+  </si>
+  <si>
+    <t>0006256778</t>
+  </si>
+  <si>
+    <t>032000</t>
+  </si>
+  <si>
+    <t>093400</t>
+  </si>
+  <si>
+    <t>4507420978-00260-0006256780</t>
+  </si>
+  <si>
+    <t>0006256780</t>
+  </si>
+  <si>
+    <t>083200</t>
+  </si>
+  <si>
+    <t>4507420978-00270-0006256781</t>
+  </si>
+  <si>
+    <t>0006256781</t>
+  </si>
+  <si>
+    <t>4507420978-00280-0006256782</t>
+  </si>
+  <si>
+    <t>0006256782</t>
+  </si>
+  <si>
+    <t>00280</t>
+  </si>
+  <si>
+    <t>4507420978-00300-0006256784</t>
+  </si>
+  <si>
+    <t>0006256784</t>
+  </si>
+  <si>
+    <t>00300</t>
+  </si>
+  <si>
+    <t>065300</t>
+  </si>
+  <si>
+    <t>4507443671-00030-0006263257</t>
+  </si>
+  <si>
+    <t>0006263257</t>
+  </si>
+  <si>
+    <t>014000</t>
+  </si>
+  <si>
+    <t>4507443671-00040-0006263258</t>
+  </si>
+  <si>
+    <t>0006263258</t>
+  </si>
+  <si>
+    <t>023000</t>
+  </si>
+  <si>
+    <t>033600</t>
+  </si>
+  <si>
+    <t>4507443671-00050-0006263259</t>
+  </si>
+  <si>
+    <t>0006263259</t>
+  </si>
+  <si>
+    <t>001700</t>
+  </si>
+  <si>
+    <t>4507443671-00060-0006263260</t>
+  </si>
+  <si>
+    <t>0006263260</t>
+  </si>
+  <si>
+    <t>4507469608-00010-0006268935</t>
+  </si>
+  <si>
+    <t>0006268935</t>
+  </si>
+  <si>
+    <t>011900</t>
+  </si>
+  <si>
+    <t>065100</t>
+  </si>
+  <si>
+    <t>4507469608-00020-0006268936</t>
+  </si>
+  <si>
+    <t>0006268936</t>
+  </si>
+  <si>
     <t>001500</t>
   </si>
   <si>
-    <t>012000</t>
-  </si>
-  <si>
-    <t>4507454607-00090-0006267239</t>
-  </si>
-  <si>
-    <t>0006267239</t>
-  </si>
-  <si>
-    <t>065600</t>
-  </si>
-  <si>
-    <t>4507454607-00100-0006267240</t>
-  </si>
-  <si>
-    <t>0006267240</t>
-  </si>
-  <si>
-    <t>4507459814-00010-0006268079</t>
-  </si>
-  <si>
-    <t>0006268079</t>
-  </si>
-  <si>
-    <t>043000</t>
-  </si>
-  <si>
-    <t>064100</t>
-  </si>
-  <si>
-    <t>4507459814-00020-0006268080</t>
-  </si>
-  <si>
-    <t>0006268080</t>
-  </si>
-  <si>
-    <t>4507459814-00030-0006268081</t>
-  </si>
-  <si>
-    <t>0006268081</t>
-  </si>
-  <si>
-    <t>032500</t>
-  </si>
-  <si>
-    <t>082100</t>
-  </si>
-  <si>
-    <t>4507459814-00040-0006268082</t>
-  </si>
-  <si>
-    <t>0006268082</t>
-  </si>
-  <si>
-    <t>062800</t>
-  </si>
-  <si>
-    <t>4507459814-00050-0006268083</t>
-  </si>
-  <si>
-    <t>0006268083</t>
-  </si>
-  <si>
-    <t>093300</t>
-  </si>
-  <si>
-    <t>4507459814-00060-0006268084</t>
-  </si>
-  <si>
-    <t>0006268084</t>
-  </si>
-  <si>
-    <t>022500</t>
-  </si>
-  <si>
-    <t>4507459814-00070-0006268085</t>
-  </si>
-  <si>
-    <t>0006268085</t>
-  </si>
-  <si>
-    <t>4507459814-00080-0006268086</t>
-  </si>
-  <si>
-    <t>0006268086</t>
-  </si>
-  <si>
-    <t>063700</t>
-  </si>
-  <si>
-    <t>4507459814-00090-0006268087</t>
-  </si>
-  <si>
-    <t>0006268087</t>
-  </si>
-  <si>
-    <t>092600</t>
-  </si>
-  <si>
-    <t>040900</t>
-  </si>
-  <si>
-    <t>4507459814-00100-0006268088</t>
-  </si>
-  <si>
-    <t>0006268088</t>
-  </si>
-  <si>
-    <t>LYNCHBURG</t>
-  </si>
-  <si>
-    <t>4507509204-00010-0006277080</t>
-  </si>
-  <si>
-    <t>0006277080</t>
-  </si>
-  <si>
-    <t>083000</t>
-  </si>
-  <si>
-    <t>4507509204-00020-0006277081</t>
-  </si>
-  <si>
-    <t>0006277081</t>
-  </si>
-  <si>
-    <t>4507523441-00050-0006279699</t>
-  </si>
-  <si>
-    <t>0006279699</t>
-  </si>
-  <si>
-    <t>043900</t>
-  </si>
-  <si>
-    <t>4507523441-00060-0006279700</t>
-  </si>
-  <si>
-    <t>0006279700</t>
-  </si>
-  <si>
-    <t>4507523940-00010-0006279776</t>
-  </si>
-  <si>
-    <t>0006279776</t>
-  </si>
-  <si>
-    <t>4507524031-00010-0006279815</t>
-  </si>
-  <si>
-    <t>0006279815</t>
-  </si>
-  <si>
-    <t>4507410004-00030-0006221876</t>
-  </si>
-  <si>
-    <t>0006221876</t>
-  </si>
-  <si>
-    <t>050900</t>
-  </si>
-  <si>
-    <t>4507410004-00050-0006221878</t>
-  </si>
-  <si>
-    <t>0006221878</t>
-  </si>
-  <si>
-    <t>072000</t>
-  </si>
-  <si>
-    <t>4507410004-00070-0006221880</t>
-  </si>
-  <si>
-    <t>0006221880</t>
-  </si>
-  <si>
-    <t>020500</t>
-  </si>
-  <si>
-    <t>4507410004-00080-0006221881</t>
-  </si>
-  <si>
-    <t>0006221881</t>
+    <t>4507469608-00070-0006268941</t>
+  </si>
+  <si>
+    <t>0006268941</t>
+  </si>
+  <si>
+    <t>033100</t>
+  </si>
+  <si>
+    <t>4507469608-00080-0006268942</t>
+  </si>
+  <si>
+    <t>0006268942</t>
+  </si>
+  <si>
+    <t>061600</t>
+  </si>
+  <si>
+    <t>4507469608-00090-0006268943</t>
+  </si>
+  <si>
+    <t>0006268943</t>
+  </si>
+  <si>
+    <t>081200</t>
+  </si>
+  <si>
+    <t>4507469608-00100-0006268944</t>
+  </si>
+  <si>
+    <t>0006268944</t>
+  </si>
+  <si>
+    <t>4507488710-00010-0006272220</t>
+  </si>
+  <si>
+    <t>0006272220</t>
+  </si>
+  <si>
+    <t>4507525630-00010-0006280083</t>
+  </si>
+  <si>
+    <t>0006280083</t>
+  </si>
+  <si>
+    <t>4507528292-00010-0006280956</t>
+  </si>
+  <si>
+    <t>0006280956</t>
+  </si>
+  <si>
+    <t>015600</t>
   </si>
   <si>
     <t>071600</t>
   </si>
   <si>
-    <t>4507410004-00090-0006221882</t>
-  </si>
-  <si>
-    <t>0006221882</t>
-  </si>
-  <si>
-    <t>4507489629-00010-0006272473</t>
-  </si>
-  <si>
-    <t>0006272473</t>
-  </si>
-  <si>
-    <t>024900</t>
-  </si>
-  <si>
-    <t>4507489629-00020-0006272474</t>
-  </si>
-  <si>
-    <t>0006272474</t>
-  </si>
-  <si>
-    <t>074200</t>
-  </si>
-  <si>
-    <t>095500</t>
-  </si>
-  <si>
-    <t>4507489629-00030-0006272475</t>
-  </si>
-  <si>
-    <t>0006272475</t>
-  </si>
-  <si>
-    <t>4507489629-00040-0006272476</t>
-  </si>
-  <si>
-    <t>0006272476</t>
-  </si>
-  <si>
-    <t>4507505041-00010-0006275972</t>
-  </si>
-  <si>
-    <t>0006275972</t>
-  </si>
-  <si>
-    <t>091400</t>
-  </si>
-  <si>
-    <t>4507523441-00010-0006279695</t>
-  </si>
-  <si>
-    <t>0006279695</t>
-  </si>
-  <si>
-    <t>014500</t>
-  </si>
-  <si>
-    <t>4507523441-00020-0006279696</t>
-  </si>
-  <si>
-    <t>0006279696</t>
-  </si>
-  <si>
-    <t>4507523441-00030-0006279697</t>
-  </si>
-  <si>
-    <t>0006279697</t>
-  </si>
-  <si>
-    <t>003000</t>
-  </si>
-  <si>
-    <t>4507523441-00040-0006279698</t>
-  </si>
-  <si>
-    <t>0006279698</t>
-  </si>
-  <si>
-    <t>021300</t>
-  </si>
-  <si>
-    <t>PERRY</t>
-  </si>
-  <si>
-    <t>4507408907-00100-0006219770</t>
-  </si>
-  <si>
-    <t>0006219770</t>
-  </si>
-  <si>
-    <t>083500</t>
-  </si>
-  <si>
-    <t>4507408907-00110-0006219771</t>
-  </si>
-  <si>
-    <t>0006219771</t>
-  </si>
-  <si>
-    <t>4507408907-00120-0006219772</t>
-  </si>
-  <si>
-    <t>0006219772</t>
-  </si>
-  <si>
-    <t>4507408907-00130-0006219773</t>
-  </si>
-  <si>
-    <t>0006219773</t>
-  </si>
-  <si>
-    <t>093000</t>
-  </si>
-  <si>
-    <t>4507408907-00140-0006219774</t>
-  </si>
-  <si>
-    <t>0006219774</t>
-  </si>
-  <si>
-    <t>4507408907-00150-0006219775</t>
-  </si>
-  <si>
-    <t>0006219775</t>
-  </si>
-  <si>
-    <t>4507408907-00160-0006219776</t>
-  </si>
-  <si>
-    <t>0006219776</t>
-  </si>
-  <si>
-    <t>4507408907-00170-0006219777</t>
-  </si>
-  <si>
-    <t>0006219777</t>
-  </si>
-  <si>
-    <t>4507408907-00180-0006219778</t>
-  </si>
-  <si>
-    <t>0006219778</t>
-  </si>
-  <si>
-    <t>4507408907-00190-0006219779</t>
-  </si>
-  <si>
-    <t>0006219779</t>
-  </si>
-  <si>
-    <t>4507487488-00010-0006271943</t>
-  </si>
-  <si>
-    <t>0006271943</t>
-  </si>
-  <si>
-    <t>SUPER PUFF</t>
-  </si>
-  <si>
-    <t>4507425196-00060-0006258828</t>
-  </si>
-  <si>
-    <t>0006258828</t>
-  </si>
-  <si>
-    <t>4507425196-00070-0006258829</t>
-  </si>
-  <si>
-    <t>0006258829</t>
-  </si>
-  <si>
-    <t>000001</t>
-  </si>
-  <si>
-    <t>4507425196-00080-0006258830</t>
-  </si>
-  <si>
-    <t>0006258830</t>
-  </si>
-  <si>
-    <t>052000</t>
-  </si>
-  <si>
-    <t>4507425196-00090-0006258831</t>
-  </si>
-  <si>
-    <t>0006258831</t>
-  </si>
-  <si>
-    <t>4507425196-00100-0006258832</t>
-  </si>
-  <si>
-    <t>0006258832</t>
-  </si>
-  <si>
-    <t>4507425196-00110-0006258833</t>
-  </si>
-  <si>
-    <t>0006258833</t>
-  </si>
-  <si>
-    <t>4507425196-00120-0006258834</t>
-  </si>
-  <si>
-    <t>0006258834</t>
-  </si>
-  <si>
-    <t>4507425196-00040-0006258826</t>
-  </si>
-  <si>
-    <t>0006258826</t>
-  </si>
-  <si>
-    <t>021700</t>
-  </si>
-  <si>
-    <t>083216</t>
-  </si>
-  <si>
-    <t>4507425196-00050-0006258827</t>
-  </si>
-  <si>
-    <t>0006258827</t>
-  </si>
-  <si>
-    <t>4507488019-00010-0006272103</t>
-  </si>
-  <si>
-    <t>0006272103</t>
-  </si>
-  <si>
-    <t>4507488019-00020-0006272104</t>
-  </si>
-  <si>
-    <t>0006272104</t>
-  </si>
-  <si>
-    <t>010702</t>
-  </si>
-  <si>
-    <t>4507488019-00030-0006272105</t>
-  </si>
-  <si>
-    <t>0006272105</t>
-  </si>
-  <si>
-    <t>4507491884-00010-0006272987</t>
-  </si>
-  <si>
-    <t>0006272987</t>
-  </si>
-  <si>
-    <t>060243</t>
-  </si>
-  <si>
-    <t>4507508326-00010-0006276419</t>
-  </si>
-  <si>
-    <t>0006276419</t>
-  </si>
-  <si>
-    <t>WATERFORD</t>
-  </si>
-  <si>
-    <t>4507425051-00110-0006258793</t>
-  </si>
-  <si>
-    <t>0006258793</t>
-  </si>
-  <si>
-    <t>4507425051-00120-0006258794</t>
-  </si>
-  <si>
-    <t>0006258794</t>
-  </si>
-  <si>
-    <t>4507425051-00130-0006258795</t>
-  </si>
-  <si>
-    <t>0006258795</t>
-  </si>
-  <si>
-    <t>4507425051-00140-0006258796</t>
-  </si>
-  <si>
-    <t>0006258796</t>
-  </si>
-  <si>
-    <t>4507425051-00150-0006258797</t>
-  </si>
-  <si>
-    <t>0006258797</t>
-  </si>
-  <si>
-    <t>4507425051-00160-0006258798</t>
-  </si>
-  <si>
-    <t>0006258798</t>
-  </si>
-  <si>
-    <t>4507425051-00170-0006258799</t>
-  </si>
-  <si>
-    <t>0006258799</t>
-  </si>
-  <si>
-    <t>4507425051-00180-0006258800</t>
-  </si>
-  <si>
-    <t>0006258800</t>
-  </si>
-  <si>
-    <t>4507425051-00190-0006258801</t>
-  </si>
-  <si>
-    <t>0006258801</t>
-  </si>
-  <si>
-    <t>4507425051-00200-0006258802</t>
-  </si>
-  <si>
-    <t>0006258802</t>
-  </si>
-  <si>
-    <t>4507425051-00210-0006258803</t>
-  </si>
-  <si>
-    <t>0006258803</t>
-  </si>
-  <si>
-    <t>4507425051-00220-0006258804</t>
-  </si>
-  <si>
-    <t>0006258804</t>
-  </si>
-  <si>
-    <t>4507425051-00230-0006258805</t>
-  </si>
-  <si>
-    <t>0006258805</t>
-  </si>
-  <si>
-    <t>00230</t>
-  </si>
-  <si>
-    <t>4507425051-00240-0006258806</t>
-  </si>
-  <si>
-    <t>0006258806</t>
-  </si>
-  <si>
-    <t>00240</t>
-  </si>
-  <si>
-    <t>4507425051-00250-0006258807</t>
-  </si>
-  <si>
-    <t>0006258807</t>
-  </si>
-  <si>
-    <t>4507439331-00160-0006262814</t>
-  </si>
-  <si>
-    <t>0006262814</t>
-  </si>
-  <si>
-    <t>4507439331-00170-0006262815</t>
-  </si>
-  <si>
-    <t>0006262815</t>
-  </si>
-  <si>
-    <t>4507439331-00180-0006262816</t>
-  </si>
-  <si>
-    <t>0006262816</t>
-  </si>
-  <si>
-    <t>4507439331-00190-0006262817</t>
-  </si>
-  <si>
-    <t>0006262817</t>
-  </si>
-  <si>
-    <t>4507439331-00200-0006262818</t>
-  </si>
-  <si>
-    <t>0006262818</t>
-  </si>
-  <si>
-    <t>4507439331-00210-0006262819</t>
-  </si>
-  <si>
-    <t>0006262819</t>
-  </si>
-  <si>
-    <t>4507439331-00220-0006262820</t>
-  </si>
-  <si>
-    <t>0006262820</t>
-  </si>
-  <si>
-    <t>MIS-BLACK GOLD FARMS</t>
-  </si>
-  <si>
-    <t>074600</t>
-  </si>
-  <si>
-    <t>074644</t>
-  </si>
-  <si>
-    <t>4507439331-00230-0006262821</t>
-  </si>
-  <si>
-    <t>0006262821</t>
-  </si>
-  <si>
-    <t>4507439331-00240-0006262822</t>
-  </si>
-  <si>
-    <t>0006262822</t>
-  </si>
-  <si>
-    <t>4507493285-00010-0006273349</t>
-  </si>
-  <si>
-    <t>0006273349</t>
-  </si>
-  <si>
-    <t>4507493285-00020-0006273350</t>
-  </si>
-  <si>
-    <t>0006273350</t>
-  </si>
-  <si>
-    <t>4507493285-00030-0006273351</t>
-  </si>
-  <si>
-    <t>0006273351</t>
-  </si>
-  <si>
-    <t>4507439331-00110-0006262809</t>
-  </si>
-  <si>
-    <t>0006262809</t>
-  </si>
-  <si>
-    <t>INW-BLACK GOLD FARMS IN 0885</t>
-  </si>
-  <si>
-    <t>4507439331-00120-0006262810</t>
-  </si>
-  <si>
-    <t>0006262810</t>
-  </si>
-  <si>
-    <t>4507439331-00130-0006262811</t>
-  </si>
-  <si>
-    <t>0006262811</t>
-  </si>
-  <si>
-    <t>4507439331-00140-0006262812</t>
-  </si>
-  <si>
-    <t>0006262812</t>
-  </si>
-  <si>
-    <t>4507439331-00150-0006262813</t>
-  </si>
-  <si>
-    <t>0006262813</t>
-  </si>
-  <si>
-    <t>INW-BLACK GOLD FARMS</t>
-  </si>
-  <si>
-    <t>4507439331-00250-0006262823</t>
-  </si>
-  <si>
-    <t>0006262823</t>
-  </si>
-  <si>
-    <t>4507493285-00040-0006273352</t>
-  </si>
-  <si>
-    <t>0006273352</t>
-  </si>
-  <si>
-    <t>WOOSTER</t>
-  </si>
-  <si>
-    <t>4507508738-00010-0006276601</t>
-  </si>
-  <si>
-    <t>0006276601</t>
-  </si>
-  <si>
-    <t>4507508738-00020-0006276602</t>
-  </si>
-  <si>
-    <t>0006276602</t>
-  </si>
-  <si>
-    <t>4507508738-00030-0006276603</t>
-  </si>
-  <si>
-    <t>0006276603</t>
-  </si>
-  <si>
-    <t>4507508738-00040-0006276604</t>
-  </si>
-  <si>
-    <t>0006276604</t>
-  </si>
-  <si>
-    <t>4507508738-00050-0006276605</t>
-  </si>
-  <si>
-    <t>0006276605</t>
-  </si>
-  <si>
-    <t>4507508738-00060-0006276606</t>
-  </si>
-  <si>
-    <t>0006276606</t>
-  </si>
-  <si>
-    <t>4507508738-00070-0006276607</t>
-  </si>
-  <si>
-    <t>0006276607</t>
-  </si>
-  <si>
-    <t>4507508738-00080-0006276608</t>
-  </si>
-  <si>
-    <t>0006276608</t>
-  </si>
-  <si>
-    <t>4507508738-00090-0006276609</t>
-  </si>
-  <si>
-    <t>0006276609</t>
-  </si>
-  <si>
-    <t>4507508738-00100-0006276610</t>
-  </si>
-  <si>
-    <t>0006276610</t>
-  </si>
-  <si>
-    <t>4507508738-00110-0006276611</t>
-  </si>
-  <si>
-    <t>0006276611</t>
-  </si>
-  <si>
-    <t>4507471133-00010-0006269152</t>
-  </si>
-  <si>
-    <t>0006269152</t>
-  </si>
-  <si>
-    <t>063000</t>
-  </si>
-  <si>
-    <t>YORK</t>
-  </si>
-  <si>
-    <t>4507420978-00170-0006256771</t>
-  </si>
-  <si>
-    <t>0006256771</t>
-  </si>
-  <si>
-    <t>095900</t>
-  </si>
-  <si>
-    <t>4507420978-00210-0006256775</t>
-  </si>
-  <si>
-    <t>0006256775</t>
-  </si>
-  <si>
-    <t>4507420978-00220-0006256776</t>
-  </si>
-  <si>
-    <t>0006256776</t>
-  </si>
-  <si>
-    <t>015400</t>
-  </si>
-  <si>
-    <t>4507420978-00230-0006256777</t>
-  </si>
-  <si>
-    <t>0006256777</t>
-  </si>
-  <si>
-    <t>040800</t>
-  </si>
-  <si>
-    <t>4507420978-00250-0006256779</t>
-  </si>
-  <si>
-    <t>0006256779</t>
-  </si>
-  <si>
-    <t>4507420978-00290-0006256783</t>
-  </si>
-  <si>
-    <t>0006256783</t>
-  </si>
-  <si>
-    <t>00290</t>
-  </si>
-  <si>
-    <t>4507420978-00310-0006256785</t>
-  </si>
-  <si>
-    <t>0006256785</t>
-  </si>
-  <si>
-    <t>00310</t>
-  </si>
-  <si>
-    <t>4507420978-00320-0006256786</t>
-  </si>
-  <si>
-    <t>0006256786</t>
-  </si>
-  <si>
-    <t>00320</t>
-  </si>
-  <si>
-    <t>4507420978-00330-0006256787</t>
-  </si>
-  <si>
-    <t>0006256787</t>
-  </si>
-  <si>
-    <t>00330</t>
-  </si>
-  <si>
-    <t>4507420978-00040-0006256758</t>
-  </si>
-  <si>
-    <t>0006256758</t>
-  </si>
-  <si>
-    <t>033400</t>
-  </si>
-  <si>
-    <t>4507420978-00050-0006256759</t>
-  </si>
-  <si>
-    <t>0006256759</t>
-  </si>
-  <si>
-    <t>054700</t>
-  </si>
-  <si>
-    <t>4507420978-00060-0006256760</t>
-  </si>
-  <si>
-    <t>0006256760</t>
-  </si>
-  <si>
-    <t>073200</t>
-  </si>
-  <si>
-    <t>4507420978-00070-0006256761</t>
-  </si>
-  <si>
-    <t>0006256761</t>
-  </si>
-  <si>
-    <t>092900</t>
-  </si>
-  <si>
-    <t>4507420978-00080-0006256762</t>
-  </si>
-  <si>
-    <t>0006256762</t>
-  </si>
-  <si>
-    <t>4507420978-00090-0006256763</t>
-  </si>
-  <si>
-    <t>0006256763</t>
-  </si>
-  <si>
-    <t>4507420978-00100-0006256764</t>
-  </si>
-  <si>
-    <t>0006256764</t>
-  </si>
-  <si>
-    <t>4507420978-00110-0006256765</t>
-  </si>
-  <si>
-    <t>0006256765</t>
-  </si>
-  <si>
-    <t>4507420978-00120-0006256766</t>
-  </si>
-  <si>
-    <t>0006256766</t>
-  </si>
-  <si>
-    <t>4507420978-00130-0006256767</t>
-  </si>
-  <si>
-    <t>0006256767</t>
-  </si>
-  <si>
-    <t>4507420978-00140-0006256768</t>
-  </si>
-  <si>
-    <t>0006256768</t>
-  </si>
-  <si>
-    <t>060400</t>
-  </si>
-  <si>
-    <t>4507420978-00150-0006256769</t>
-  </si>
-  <si>
-    <t>0006256769</t>
-  </si>
-  <si>
-    <t>023800</t>
-  </si>
-  <si>
-    <t>081100</t>
-  </si>
-  <si>
-    <t>4507420978-00160-0006256770</t>
-  </si>
-  <si>
-    <t>0006256770</t>
-  </si>
-  <si>
-    <t>052300</t>
-  </si>
-  <si>
-    <t>4507420978-00180-0006256772</t>
-  </si>
-  <si>
-    <t>0006256772</t>
-  </si>
-  <si>
-    <t>4507420978-00190-0006256773</t>
-  </si>
-  <si>
-    <t>0006256773</t>
-  </si>
-  <si>
-    <t>4507420978-00200-0006256774</t>
-  </si>
-  <si>
-    <t>0006256774</t>
-  </si>
-  <si>
-    <t>4507420978-00240-0006256778</t>
-  </si>
-  <si>
-    <t>0006256778</t>
-  </si>
-  <si>
-    <t>032000</t>
-  </si>
-  <si>
-    <t>093400</t>
-  </si>
-  <si>
-    <t>4507420978-00260-0006256780</t>
-  </si>
-  <si>
-    <t>0006256780</t>
-  </si>
-  <si>
-    <t>083200</t>
-  </si>
-  <si>
-    <t>4507420978-00270-0006256781</t>
-  </si>
-  <si>
-    <t>0006256781</t>
-  </si>
-  <si>
-    <t>4507420978-00280-0006256782</t>
-  </si>
-  <si>
-    <t>0006256782</t>
-  </si>
-  <si>
-    <t>00280</t>
-  </si>
-  <si>
-    <t>4507420978-00300-0006256784</t>
-  </si>
-  <si>
-    <t>0006256784</t>
-  </si>
-  <si>
-    <t>00300</t>
-  </si>
-  <si>
-    <t>065300</t>
-  </si>
-  <si>
-    <t>4507443671-00030-0006263257</t>
-  </si>
-  <si>
-    <t>0006263257</t>
-  </si>
-  <si>
-    <t>014000</t>
-  </si>
-  <si>
-    <t>4507443671-00040-0006263258</t>
-  </si>
-  <si>
-    <t>0006263258</t>
-  </si>
-  <si>
-    <t>023000</t>
-  </si>
-  <si>
-    <t>033600</t>
-  </si>
-  <si>
-    <t>4507443671-00050-0006263259</t>
-  </si>
-  <si>
-    <t>0006263259</t>
-  </si>
-  <si>
-    <t>001700</t>
-  </si>
-  <si>
-    <t>4507443671-00060-0006263260</t>
-  </si>
-  <si>
-    <t>0006263260</t>
-  </si>
-  <si>
-    <t>4507469608-00010-0006268935</t>
-  </si>
-  <si>
-    <t>0006268935</t>
-  </si>
-  <si>
-    <t>011900</t>
-  </si>
-  <si>
-    <t>065100</t>
-  </si>
-  <si>
-    <t>4507469608-00020-0006268936</t>
-  </si>
-  <si>
-    <t>0006268936</t>
-  </si>
-  <si>
-    <t>4507469608-00070-0006268941</t>
-  </si>
-  <si>
-    <t>0006268941</t>
-  </si>
-  <si>
-    <t>033100</t>
-  </si>
-  <si>
-    <t>4507469608-00080-0006268942</t>
-  </si>
-  <si>
-    <t>0006268942</t>
-  </si>
-  <si>
-    <t>061600</t>
-  </si>
-  <si>
-    <t>4507469608-00090-0006268943</t>
-  </si>
-  <si>
-    <t>0006268943</t>
-  </si>
-  <si>
-    <t>081200</t>
-  </si>
-  <si>
-    <t>4507469608-00100-0006268944</t>
-  </si>
-  <si>
-    <t>0006268944</t>
-  </si>
-  <si>
-    <t>4507488710-00010-0006272220</t>
-  </si>
-  <si>
-    <t>0006272220</t>
-  </si>
-  <si>
-    <t>4507525630-00010-0006280083</t>
-  </si>
-  <si>
-    <t>0006280083</t>
-  </si>
-  <si>
-    <t>4507528292-00010-0006280956</t>
-  </si>
-  <si>
-    <t>0006280956</t>
-  </si>
-  <si>
-    <t>015600</t>
-  </si>
-  <si>
     <t>INW</t>
   </si>
   <si>
+    <t>MIS</t>
+  </si>
+  <si>
     <t>MDR</t>
-  </si>
-  <si>
-    <t>MIS</t>
   </si>
 </sst>
 </file>
@@ -2713,10 +2713,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3033,12 +3029,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F50CD2-FD3B-47DB-AA7D-C7DA447965F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19312C60-E983-4A2F-9A4D-C37E2F26DB41}">
   <dimension ref="A1:EL205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:142" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -4932,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V16" t="s">
         <v>205</v>
@@ -4944,7 +4937,7 @@
         <v>152</v>
       </c>
       <c r="Y16" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z16" t="s">
         <v>152</v>
@@ -5030,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V17" t="s">
         <v>205</v>
@@ -5042,7 +5035,7 @@
         <v>152</v>
       </c>
       <c r="Y17" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z17" t="s">
         <v>152</v>
@@ -5128,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V18" t="s">
         <v>205</v>
@@ -5140,7 +5133,7 @@
         <v>152</v>
       </c>
       <c r="Y18" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z18" t="s">
         <v>152</v>
@@ -5226,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V19" t="s">
         <v>205</v>
@@ -5238,7 +5231,7 @@
         <v>152</v>
       </c>
       <c r="Y19" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z19" t="s">
         <v>152</v>
@@ -5324,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V20" t="s">
         <v>205</v>
@@ -5336,7 +5329,7 @@
         <v>152</v>
       </c>
       <c r="Y20" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z20" t="s">
         <v>152</v>
@@ -5422,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V21" t="s">
         <v>205</v>
@@ -5434,7 +5427,7 @@
         <v>152</v>
       </c>
       <c r="Y21" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z21" t="s">
         <v>152</v>
@@ -5520,7 +5513,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V22" t="s">
         <v>205</v>
@@ -5532,7 +5525,7 @@
         <v>152</v>
       </c>
       <c r="Y22" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z22" t="s">
         <v>152</v>
@@ -5618,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V23" t="s">
         <v>205</v>
@@ -5630,7 +5623,7 @@
         <v>152</v>
       </c>
       <c r="Y23" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z23" t="s">
         <v>152</v>
@@ -5716,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V24" t="s">
         <v>205</v>
@@ -5728,7 +5721,7 @@
         <v>152</v>
       </c>
       <c r="Y24" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z24" t="s">
         <v>152</v>
@@ -5814,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V25" t="s">
         <v>205</v>
@@ -5826,7 +5819,7 @@
         <v>152</v>
       </c>
       <c r="Y25" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z25" t="s">
         <v>152</v>
@@ -5912,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V26" t="s">
         <v>205</v>
@@ -5924,7 +5917,7 @@
         <v>152</v>
       </c>
       <c r="Y26" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z26" t="s">
         <v>152</v>
@@ -6302,7 +6295,7 @@
         <v>2026</v>
       </c>
       <c r="T29" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V29" t="s">
         <v>205</v>
@@ -6314,7 +6307,7 @@
         <v>152</v>
       </c>
       <c r="Y29" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z29" t="s">
         <v>152</v>
@@ -6454,7 +6447,7 @@
         <v>2026</v>
       </c>
       <c r="T30" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V30" t="s">
         <v>205</v>
@@ -6466,7 +6459,7 @@
         <v>152</v>
       </c>
       <c r="Y30" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z30" t="s">
         <v>152</v>
@@ -9335,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V50" t="s">
         <v>315</v>
@@ -9347,7 +9340,7 @@
         <v>152</v>
       </c>
       <c r="Y50" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z50" t="s">
         <v>152</v>
@@ -9448,7 +9441,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V51" t="s">
         <v>315</v>
@@ -9460,7 +9453,7 @@
         <v>152</v>
       </c>
       <c r="Y51" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z51" t="s">
         <v>152</v>
@@ -9597,7 +9590,7 @@
         <v>2026</v>
       </c>
       <c r="T52" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V52" t="s">
         <v>315</v>
@@ -9609,7 +9602,7 @@
         <v>152</v>
       </c>
       <c r="Y52" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z52" t="s">
         <v>152</v>
@@ -9761,7 +9754,7 @@
         <v>2026</v>
       </c>
       <c r="T53" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V53" t="s">
         <v>315</v>
@@ -9773,7 +9766,7 @@
         <v>152</v>
       </c>
       <c r="Y53" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z53" t="s">
         <v>152</v>
@@ -9925,7 +9918,7 @@
         <v>2026</v>
       </c>
       <c r="T54" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V54" t="s">
         <v>315</v>
@@ -9937,7 +9930,7 @@
         <v>152</v>
       </c>
       <c r="Y54" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z54" t="s">
         <v>152</v>
@@ -10089,7 +10082,7 @@
         <v>2026</v>
       </c>
       <c r="T55" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V55" t="s">
         <v>315</v>
@@ -10101,7 +10094,7 @@
         <v>152</v>
       </c>
       <c r="Y55" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z55" t="s">
         <v>152</v>
@@ -10253,7 +10246,7 @@
         <v>2026</v>
       </c>
       <c r="T56" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V56" t="s">
         <v>315</v>
@@ -10265,7 +10258,7 @@
         <v>152</v>
       </c>
       <c r="Y56" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z56" t="s">
         <v>152</v>
@@ -10417,7 +10410,7 @@
         <v>2026</v>
       </c>
       <c r="T57" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V57" t="s">
         <v>315</v>
@@ -10429,7 +10422,7 @@
         <v>152</v>
       </c>
       <c r="Y57" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z57" t="s">
         <v>152</v>
@@ -10581,7 +10574,7 @@
         <v>2026</v>
       </c>
       <c r="T58" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V58" t="s">
         <v>315</v>
@@ -10593,7 +10586,7 @@
         <v>152</v>
       </c>
       <c r="Y58" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z58" t="s">
         <v>152</v>
@@ -10745,7 +10738,7 @@
         <v>2026</v>
       </c>
       <c r="T59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V59" t="s">
         <v>315</v>
@@ -10757,7 +10750,7 @@
         <v>152</v>
       </c>
       <c r="Y59" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z59" t="s">
         <v>152</v>
@@ -10787,7 +10780,7 @@
         <v>20260815</v>
       </c>
       <c r="AL59" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AM59">
         <v>8132026</v>
@@ -10882,13 +10875,13 @@
         <v>249</v>
       </c>
       <c r="G60" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H60" t="s">
         <v>145</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J60">
         <v>4507454607</v>
@@ -10909,7 +10902,7 @@
         <v>2026</v>
       </c>
       <c r="T60" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V60" t="s">
         <v>315</v>
@@ -10921,7 +10914,7 @@
         <v>152</v>
       </c>
       <c r="Y60" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z60" t="s">
         <v>152</v>
@@ -10951,7 +10944,7 @@
         <v>20260815</v>
       </c>
       <c r="AL60" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM60">
         <v>8132026</v>
@@ -11046,13 +11039,13 @@
         <v>249</v>
       </c>
       <c r="G61" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H61" t="s">
         <v>145</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J61">
         <v>4507454607</v>
@@ -11073,7 +11066,7 @@
         <v>2026</v>
       </c>
       <c r="T61" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V61" t="s">
         <v>315</v>
@@ -11085,7 +11078,7 @@
         <v>152</v>
       </c>
       <c r="Y61" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z61" t="s">
         <v>152</v>
@@ -11210,13 +11203,13 @@
         <v>249</v>
       </c>
       <c r="G62" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H62" t="s">
         <v>145</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J62">
         <v>4507459814</v>
@@ -11237,7 +11230,7 @@
         <v>2026</v>
       </c>
       <c r="T62" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V62" t="s">
         <v>315</v>
@@ -11249,7 +11242,7 @@
         <v>152</v>
       </c>
       <c r="Y62" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z62" t="s">
         <v>152</v>
@@ -11273,13 +11266,13 @@
         <v>20260811</v>
       </c>
       <c r="AJ62" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AK62">
         <v>20260811</v>
       </c>
       <c r="AL62" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AP62" t="s">
         <v>165</v>
@@ -11365,13 +11358,13 @@
         <v>249</v>
       </c>
       <c r="G63" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H63" t="s">
         <v>145</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J63">
         <v>4507459814</v>
@@ -11392,7 +11385,7 @@
         <v>2026</v>
       </c>
       <c r="T63" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V63" t="s">
         <v>315</v>
@@ -11404,7 +11397,7 @@
         <v>152</v>
       </c>
       <c r="Y63" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z63" t="s">
         <v>152</v>
@@ -11529,13 +11522,13 @@
         <v>249</v>
       </c>
       <c r="G64" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H64" t="s">
         <v>145</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J64">
         <v>4507459814</v>
@@ -11556,7 +11549,7 @@
         <v>2026</v>
       </c>
       <c r="T64" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V64" t="s">
         <v>315</v>
@@ -11568,7 +11561,7 @@
         <v>152</v>
       </c>
       <c r="Y64" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z64" t="s">
         <v>152</v>
@@ -11592,13 +11585,13 @@
         <v>20260812</v>
       </c>
       <c r="AJ64" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AK64">
         <v>20260812</v>
       </c>
       <c r="AL64" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AM64">
         <v>8112026</v>
@@ -11693,13 +11686,13 @@
         <v>249</v>
       </c>
       <c r="G65" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H65" t="s">
         <v>145</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J65">
         <v>4507459814</v>
@@ -11720,7 +11713,7 @@
         <v>2026</v>
       </c>
       <c r="T65" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V65" t="s">
         <v>315</v>
@@ -11732,7 +11725,7 @@
         <v>152</v>
       </c>
       <c r="Y65" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z65" t="s">
         <v>152</v>
@@ -11756,7 +11749,7 @@
         <v>20260812</v>
       </c>
       <c r="AJ65" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AK65">
         <v>20260812</v>
@@ -11857,13 +11850,13 @@
         <v>249</v>
       </c>
       <c r="G66" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H66" t="s">
         <v>145</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J66">
         <v>4507459814</v>
@@ -11884,7 +11877,7 @@
         <v>2026</v>
       </c>
       <c r="T66" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V66" t="s">
         <v>315</v>
@@ -11896,7 +11889,7 @@
         <v>152</v>
       </c>
       <c r="Y66" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z66" t="s">
         <v>152</v>
@@ -11920,7 +11913,7 @@
         <v>20260812</v>
       </c>
       <c r="AJ66" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AK66">
         <v>20260812</v>
@@ -12012,13 +12005,13 @@
         <v>249</v>
       </c>
       <c r="G67" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H67" t="s">
         <v>145</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J67">
         <v>4507459814</v>
@@ -12039,7 +12032,7 @@
         <v>2026</v>
       </c>
       <c r="T67" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V67" t="s">
         <v>315</v>
@@ -12051,7 +12044,7 @@
         <v>152</v>
       </c>
       <c r="Y67" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z67" t="s">
         <v>152</v>
@@ -12081,7 +12074,7 @@
         <v>20260813</v>
       </c>
       <c r="AL67" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AM67">
         <v>8112026</v>
@@ -12176,13 +12169,13 @@
         <v>249</v>
       </c>
       <c r="G68" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H68" t="s">
         <v>145</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J68">
         <v>4507459814</v>
@@ -12203,7 +12196,7 @@
         <v>2026</v>
       </c>
       <c r="T68" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V68" t="s">
         <v>315</v>
@@ -12215,7 +12208,7 @@
         <v>152</v>
       </c>
       <c r="Y68" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z68" t="s">
         <v>152</v>
@@ -12340,13 +12333,13 @@
         <v>249</v>
       </c>
       <c r="G69" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H69" t="s">
         <v>145</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J69">
         <v>4507459814</v>
@@ -12367,7 +12360,7 @@
         <v>2026</v>
       </c>
       <c r="T69" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V69" t="s">
         <v>315</v>
@@ -12379,7 +12372,7 @@
         <v>152</v>
       </c>
       <c r="Y69" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z69" t="s">
         <v>152</v>
@@ -12403,7 +12396,7 @@
         <v>20260813</v>
       </c>
       <c r="AJ69" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AK69">
         <v>20260813</v>
@@ -12504,13 +12497,13 @@
         <v>249</v>
       </c>
       <c r="G70" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H70" t="s">
         <v>145</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J70">
         <v>4507459814</v>
@@ -12531,7 +12524,7 @@
         <v>2026</v>
       </c>
       <c r="T70" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V70" t="s">
         <v>315</v>
@@ -12543,7 +12536,7 @@
         <v>152</v>
       </c>
       <c r="Y70" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z70" t="s">
         <v>152</v>
@@ -12567,13 +12560,13 @@
         <v>20260813</v>
       </c>
       <c r="AJ70" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AK70">
         <v>20260814</v>
       </c>
       <c r="AL70" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM70">
         <v>8122026</v>
@@ -12668,13 +12661,13 @@
         <v>249</v>
       </c>
       <c r="G71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H71" t="s">
         <v>145</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J71">
         <v>4507459814</v>
@@ -12695,7 +12688,7 @@
         <v>2026</v>
       </c>
       <c r="T71" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="V71" t="s">
         <v>315</v>
@@ -12707,7 +12700,7 @@
         <v>152</v>
       </c>
       <c r="Y71" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Z71" t="s">
         <v>152</v>
@@ -12823,19 +12816,19 @@
         <v>2100</v>
       </c>
       <c r="E72" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F72" t="s">
         <v>249</v>
       </c>
       <c r="G72" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H72" t="s">
         <v>145</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="J72">
         <v>4507509204</v>
@@ -12856,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="T72" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V72" t="s">
         <v>205</v>
@@ -12868,7 +12861,7 @@
         <v>152</v>
       </c>
       <c r="Y72" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z72" t="s">
         <v>152</v>
@@ -12883,7 +12876,7 @@
         <v>20260817</v>
       </c>
       <c r="AH72" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AM72">
         <v>8</v>
@@ -12939,19 +12932,19 @@
         <v>2100</v>
       </c>
       <c r="E73" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F73" t="s">
         <v>249</v>
       </c>
       <c r="G73" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H73" t="s">
         <v>145</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J73">
         <v>4507509204</v>
@@ -12972,7 +12965,7 @@
         <v>0</v>
       </c>
       <c r="T73" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V73" t="s">
         <v>205</v>
@@ -12984,7 +12977,7 @@
         <v>152</v>
       </c>
       <c r="Y73" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z73" t="s">
         <v>152</v>
@@ -13055,19 +13048,19 @@
         <v>2100</v>
       </c>
       <c r="E74" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F74" t="s">
         <v>249</v>
       </c>
       <c r="G74" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H74" t="s">
         <v>145</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J74">
         <v>4507523441</v>
@@ -13127,7 +13120,7 @@
         <v>20260816</v>
       </c>
       <c r="AL74" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AM74">
         <v>8142026</v>
@@ -13216,19 +13209,19 @@
         <v>2100</v>
       </c>
       <c r="E75" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F75" t="s">
         <v>249</v>
       </c>
       <c r="G75" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H75" t="s">
         <v>145</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J75">
         <v>4507523441</v>
@@ -13335,19 +13328,19 @@
         <v>2100</v>
       </c>
       <c r="E76" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F76" t="s">
         <v>249</v>
       </c>
       <c r="G76" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H76" t="s">
         <v>145</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J76">
         <v>4507523940</v>
@@ -13368,7 +13361,7 @@
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V76" t="s">
         <v>205</v>
@@ -13380,7 +13373,7 @@
         <v>152</v>
       </c>
       <c r="Y76" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z76" t="s">
         <v>152</v>
@@ -13451,19 +13444,19 @@
         <v>2100</v>
       </c>
       <c r="E77" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F77" t="s">
         <v>249</v>
       </c>
       <c r="G77" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H77" t="s">
         <v>145</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J77">
         <v>4507524031</v>
@@ -13484,7 +13477,7 @@
         <v>0</v>
       </c>
       <c r="T77" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V77" t="s">
         <v>205</v>
@@ -13496,7 +13489,7 @@
         <v>152</v>
       </c>
       <c r="Y77" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z77" t="s">
         <v>152</v>
@@ -13567,19 +13560,19 @@
         <v>2100</v>
       </c>
       <c r="E78" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F78" t="s">
         <v>249</v>
       </c>
       <c r="G78" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H78" t="s">
         <v>145</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="J78">
         <v>4507410004</v>
@@ -13600,7 +13593,7 @@
         <v>2026</v>
       </c>
       <c r="T78" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V78" t="s">
         <v>205</v>
@@ -13612,7 +13605,7 @@
         <v>152</v>
       </c>
       <c r="Y78" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z78" t="s">
         <v>152</v>
@@ -13642,7 +13635,7 @@
         <v>20260814</v>
       </c>
       <c r="AL78" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AM78">
         <v>8</v>
@@ -13728,19 +13721,19 @@
         <v>2100</v>
       </c>
       <c r="E79" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F79" t="s">
         <v>249</v>
       </c>
       <c r="G79" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H79" t="s">
         <v>145</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J79">
         <v>4507410004</v>
@@ -13761,7 +13754,7 @@
         <v>2026</v>
       </c>
       <c r="T79" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V79" t="s">
         <v>205</v>
@@ -13773,7 +13766,7 @@
         <v>152</v>
       </c>
       <c r="Y79" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z79" t="s">
         <v>152</v>
@@ -13803,7 +13796,7 @@
         <v>20260814</v>
       </c>
       <c r="AL79" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM79">
         <v>8</v>
@@ -13889,19 +13882,19 @@
         <v>2100</v>
       </c>
       <c r="E80" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F80" t="s">
         <v>249</v>
       </c>
       <c r="G80" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H80" t="s">
         <v>145</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J80">
         <v>4507410004</v>
@@ -13922,7 +13915,7 @@
         <v>2026</v>
       </c>
       <c r="T80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V80" t="s">
         <v>205</v>
@@ -13934,7 +13927,7 @@
         <v>152</v>
       </c>
       <c r="Y80" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z80" t="s">
         <v>152</v>
@@ -13958,7 +13951,7 @@
         <v>20260814</v>
       </c>
       <c r="AJ80" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AK80">
         <v>20260814</v>
@@ -14050,19 +14043,19 @@
         <v>2100</v>
       </c>
       <c r="E81" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F81" t="s">
         <v>249</v>
       </c>
       <c r="G81" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H81" t="s">
         <v>145</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J81">
         <v>4507410004</v>
@@ -14083,7 +14076,7 @@
         <v>2026</v>
       </c>
       <c r="T81" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V81" t="s">
         <v>205</v>
@@ -14095,7 +14088,7 @@
         <v>152</v>
       </c>
       <c r="Y81" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z81" t="s">
         <v>152</v>
@@ -14119,7 +14112,7 @@
         <v>20260814</v>
       </c>
       <c r="AJ81" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AK81">
         <v>20260814</v>
@@ -14211,19 +14204,19 @@
         <v>2100</v>
       </c>
       <c r="E82" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F82" t="s">
         <v>249</v>
       </c>
       <c r="G82" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H82" t="s">
         <v>145</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J82">
         <v>4507410004</v>
@@ -14244,7 +14237,7 @@
         <v>2026</v>
       </c>
       <c r="T82" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V82" t="s">
         <v>205</v>
@@ -14256,7 +14249,7 @@
         <v>152</v>
       </c>
       <c r="Y82" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z82" t="s">
         <v>152</v>
@@ -14372,19 +14365,19 @@
         <v>2100</v>
       </c>
       <c r="E83" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F83" t="s">
         <v>249</v>
       </c>
       <c r="G83" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="H83" t="s">
         <v>145</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="J83">
         <v>4507489629</v>
@@ -14405,7 +14398,7 @@
         <v>2026</v>
       </c>
       <c r="T83" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V83" t="s">
         <v>205</v>
@@ -14417,7 +14410,7 @@
         <v>152</v>
       </c>
       <c r="Y83" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z83" t="s">
         <v>152</v>
@@ -14447,7 +14440,7 @@
         <v>20260815</v>
       </c>
       <c r="AL83" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AM83">
         <v>8</v>
@@ -14533,19 +14526,19 @@
         <v>2100</v>
       </c>
       <c r="E84" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F84" t="s">
         <v>249</v>
       </c>
       <c r="G84" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H84" t="s">
         <v>145</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="J84">
         <v>4507489629</v>
@@ -14566,7 +14559,7 @@
         <v>2026</v>
       </c>
       <c r="T84" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V84" t="s">
         <v>205</v>
@@ -14578,7 +14571,7 @@
         <v>152</v>
       </c>
       <c r="Y84" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z84" t="s">
         <v>152</v>
@@ -14602,13 +14595,13 @@
         <v>20260814</v>
       </c>
       <c r="AJ84" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AK84">
         <v>20260815</v>
       </c>
       <c r="AL84" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AM84">
         <v>8</v>
@@ -14694,19 +14687,19 @@
         <v>2100</v>
       </c>
       <c r="E85" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F85" t="s">
         <v>249</v>
       </c>
       <c r="G85" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="H85" t="s">
         <v>145</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J85">
         <v>4507489629</v>
@@ -14727,7 +14720,7 @@
         <v>2026</v>
       </c>
       <c r="T85" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V85" t="s">
         <v>205</v>
@@ -14739,7 +14732,7 @@
         <v>152</v>
       </c>
       <c r="Y85" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z85" t="s">
         <v>152</v>
@@ -14855,19 +14848,19 @@
         <v>2100</v>
       </c>
       <c r="E86" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F86" t="s">
         <v>249</v>
       </c>
       <c r="G86" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H86" t="s">
         <v>145</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J86">
         <v>4507489629</v>
@@ -14888,7 +14881,7 @@
         <v>2026</v>
       </c>
       <c r="T86" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V86" t="s">
         <v>205</v>
@@ -14900,7 +14893,7 @@
         <v>152</v>
       </c>
       <c r="Y86" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z86" t="s">
         <v>152</v>
@@ -15016,19 +15009,19 @@
         <v>2100</v>
       </c>
       <c r="E87" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F87" t="s">
         <v>249</v>
       </c>
       <c r="G87" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="H87" t="s">
         <v>145</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J87">
         <v>4507505041</v>
@@ -15049,7 +15042,7 @@
         <v>2026</v>
       </c>
       <c r="T87" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V87" t="s">
         <v>205</v>
@@ -15061,7 +15054,7 @@
         <v>152</v>
       </c>
       <c r="Y87" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z87" t="s">
         <v>152</v>
@@ -15085,7 +15078,7 @@
         <v>20260815</v>
       </c>
       <c r="AJ87" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AK87">
         <v>20260815</v>
@@ -15177,19 +15170,19 @@
         <v>2100</v>
       </c>
       <c r="E88" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F88" t="s">
         <v>249</v>
       </c>
       <c r="G88" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="H88" t="s">
         <v>145</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J88">
         <v>4507523441</v>
@@ -15246,7 +15239,7 @@
         <v>20260815</v>
       </c>
       <c r="AJ88" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AK88">
         <v>20260815</v>
@@ -15341,19 +15334,19 @@
         <v>2100</v>
       </c>
       <c r="E89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F89" t="s">
         <v>249</v>
       </c>
       <c r="G89" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="H89" t="s">
         <v>145</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J89">
         <v>4507523441</v>
@@ -15505,19 +15498,19 @@
         <v>2100</v>
       </c>
       <c r="E90" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F90" t="s">
         <v>249</v>
       </c>
       <c r="G90" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H90" t="s">
         <v>145</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J90">
         <v>4507523441</v>
@@ -15580,7 +15573,7 @@
         <v>20260816</v>
       </c>
       <c r="AL90" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AM90">
         <v>8142026</v>
@@ -15669,19 +15662,19 @@
         <v>2100</v>
       </c>
       <c r="E91" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F91" t="s">
         <v>249</v>
       </c>
       <c r="G91" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="H91" t="s">
         <v>145</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="J91">
         <v>4507523441</v>
@@ -15744,7 +15737,7 @@
         <v>20260816</v>
       </c>
       <c r="AL91" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AM91">
         <v>8142026</v>
@@ -15833,19 +15826,19 @@
         <v>2018</v>
       </c>
       <c r="E92" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F92" t="s">
         <v>249</v>
       </c>
       <c r="G92" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H92" t="s">
         <v>145</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J92">
         <v>4507408907</v>
@@ -15866,7 +15859,7 @@
         <v>2026</v>
       </c>
       <c r="T92" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V92" t="s">
         <v>205</v>
@@ -15878,7 +15871,7 @@
         <v>152</v>
       </c>
       <c r="Y92" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z92" t="s">
         <v>152</v>
@@ -15902,7 +15895,7 @@
         <v>20260811</v>
       </c>
       <c r="AJ92" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AK92">
         <v>20260811</v>
@@ -15994,19 +15987,19 @@
         <v>2018</v>
       </c>
       <c r="E93" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F93" t="s">
         <v>249</v>
       </c>
       <c r="G93" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H93" t="s">
         <v>145</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J93">
         <v>4507408907</v>
@@ -16027,7 +16020,7 @@
         <v>2026</v>
       </c>
       <c r="T93" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V93" t="s">
         <v>205</v>
@@ -16039,7 +16032,7 @@
         <v>152</v>
       </c>
       <c r="Y93" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z93" t="s">
         <v>152</v>
@@ -16155,19 +16148,19 @@
         <v>2018</v>
       </c>
       <c r="E94" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F94" t="s">
         <v>249</v>
       </c>
       <c r="G94" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="H94" t="s">
         <v>145</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="J94">
         <v>4507408907</v>
@@ -16188,7 +16181,7 @@
         <v>2026</v>
       </c>
       <c r="T94" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V94" t="s">
         <v>205</v>
@@ -16200,7 +16193,7 @@
         <v>152</v>
       </c>
       <c r="Y94" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z94" t="s">
         <v>152</v>
@@ -16316,19 +16309,19 @@
         <v>2018</v>
       </c>
       <c r="E95" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F95" t="s">
         <v>249</v>
       </c>
       <c r="G95" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="H95" t="s">
         <v>145</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="J95">
         <v>4507408907</v>
@@ -16349,7 +16342,7 @@
         <v>2026</v>
       </c>
       <c r="T95" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V95" t="s">
         <v>205</v>
@@ -16361,7 +16354,7 @@
         <v>152</v>
       </c>
       <c r="Y95" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z95" t="s">
         <v>152</v>
@@ -16477,19 +16470,19 @@
         <v>2018</v>
       </c>
       <c r="E96" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F96" t="s">
         <v>249</v>
       </c>
       <c r="G96" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H96" t="s">
         <v>145</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J96">
         <v>4507408907</v>
@@ -16510,7 +16503,7 @@
         <v>2026</v>
       </c>
       <c r="T96" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V96" t="s">
         <v>205</v>
@@ -16522,7 +16515,7 @@
         <v>152</v>
       </c>
       <c r="Y96" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z96" t="s">
         <v>152</v>
@@ -16614,19 +16607,19 @@
         <v>2018</v>
       </c>
       <c r="E97" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F97" t="s">
         <v>249</v>
       </c>
       <c r="G97" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H97" t="s">
         <v>145</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J97">
         <v>4507408907</v>
@@ -16647,7 +16640,7 @@
         <v>2026</v>
       </c>
       <c r="T97" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V97" t="s">
         <v>205</v>
@@ -16659,7 +16652,7 @@
         <v>152</v>
       </c>
       <c r="Y97" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z97" t="s">
         <v>152</v>
@@ -16775,19 +16768,19 @@
         <v>2018</v>
       </c>
       <c r="E98" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F98" t="s">
         <v>249</v>
       </c>
       <c r="G98" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="H98" t="s">
         <v>145</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J98">
         <v>4507408907</v>
@@ -16808,7 +16801,7 @@
         <v>2026</v>
       </c>
       <c r="T98" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V98" t="s">
         <v>205</v>
@@ -16820,7 +16813,7 @@
         <v>152</v>
       </c>
       <c r="Y98" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z98" t="s">
         <v>152</v>
@@ -16933,19 +16926,19 @@
         <v>2018</v>
       </c>
       <c r="E99" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F99" t="s">
         <v>249</v>
       </c>
       <c r="G99" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H99" t="s">
         <v>145</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J99">
         <v>4507408907</v>
@@ -16966,7 +16959,7 @@
         <v>2026</v>
       </c>
       <c r="T99" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V99" t="s">
         <v>205</v>
@@ -16978,7 +16971,7 @@
         <v>152</v>
       </c>
       <c r="Y99" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z99" t="s">
         <v>152</v>
@@ -17094,19 +17087,19 @@
         <v>2018</v>
       </c>
       <c r="E100" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F100" t="s">
         <v>249</v>
       </c>
       <c r="G100" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="H100" t="s">
         <v>145</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="J100">
         <v>4507408907</v>
@@ -17127,7 +17120,7 @@
         <v>2026</v>
       </c>
       <c r="T100" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V100" t="s">
         <v>205</v>
@@ -17139,7 +17132,7 @@
         <v>152</v>
       </c>
       <c r="Y100" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z100" t="s">
         <v>152</v>
@@ -17255,19 +17248,19 @@
         <v>2018</v>
       </c>
       <c r="E101" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F101" t="s">
         <v>249</v>
       </c>
       <c r="G101" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="H101" t="s">
         <v>145</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J101">
         <v>4507408907</v>
@@ -17288,7 +17281,7 @@
         <v>2026</v>
       </c>
       <c r="T101" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V101" t="s">
         <v>205</v>
@@ -17300,7 +17293,7 @@
         <v>152</v>
       </c>
       <c r="Y101" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z101" t="s">
         <v>152</v>
@@ -17416,19 +17409,19 @@
         <v>2018</v>
       </c>
       <c r="E102" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F102" t="s">
         <v>249</v>
       </c>
       <c r="G102" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="H102" t="s">
         <v>145</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J102">
         <v>4507487488</v>
@@ -17449,7 +17442,7 @@
         <v>2026</v>
       </c>
       <c r="T102" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V102" t="s">
         <v>205</v>
@@ -17461,7 +17454,7 @@
         <v>152</v>
       </c>
       <c r="Y102" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z102" t="s">
         <v>152</v>
@@ -17577,19 +17570,19 @@
         <v>2474</v>
       </c>
       <c r="E103" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F103" t="s">
         <v>143</v>
       </c>
       <c r="G103" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="H103" t="s">
         <v>145</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J103">
         <v>4507425196</v>
@@ -17675,19 +17668,19 @@
         <v>2474</v>
       </c>
       <c r="E104" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F104" t="s">
         <v>143</v>
       </c>
       <c r="G104" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H104" t="s">
         <v>145</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J104">
         <v>4507425196</v>
@@ -17732,7 +17725,7 @@
         <v>20260813</v>
       </c>
       <c r="AH104" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AU104" t="s">
         <v>154</v>
@@ -17773,19 +17766,19 @@
         <v>2474</v>
       </c>
       <c r="E105" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F105" t="s">
         <v>143</v>
       </c>
       <c r="G105" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H105" t="s">
         <v>145</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J105">
         <v>4507425196</v>
@@ -17830,7 +17823,7 @@
         <v>20260813</v>
       </c>
       <c r="AH105" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AU105" t="s">
         <v>154</v>
@@ -17871,19 +17864,19 @@
         <v>2474</v>
       </c>
       <c r="E106" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F106" t="s">
         <v>143</v>
       </c>
       <c r="G106" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H106" t="s">
         <v>145</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J106">
         <v>4507425196</v>
@@ -17969,19 +17962,19 @@
         <v>2474</v>
       </c>
       <c r="E107" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F107" t="s">
         <v>143</v>
       </c>
       <c r="G107" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="H107" t="s">
         <v>145</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J107">
         <v>4507425196</v>
@@ -18026,7 +18019,7 @@
         <v>20260814</v>
       </c>
       <c r="AH107" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AU107" t="s">
         <v>154</v>
@@ -18067,19 +18060,19 @@
         <v>2474</v>
       </c>
       <c r="E108" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F108" t="s">
         <v>143</v>
       </c>
       <c r="G108" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H108" t="s">
         <v>145</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J108">
         <v>4507425196</v>
@@ -18165,19 +18158,19 @@
         <v>2474</v>
       </c>
       <c r="E109" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F109" t="s">
         <v>143</v>
       </c>
       <c r="G109" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H109" t="s">
         <v>145</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="J109">
         <v>4507425196</v>
@@ -18263,19 +18256,19 @@
         <v>2474</v>
       </c>
       <c r="E110" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F110" t="s">
         <v>143</v>
       </c>
       <c r="G110" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="H110" t="s">
         <v>145</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J110">
         <v>4507425196</v>
@@ -18332,13 +18325,13 @@
         <v>20260812</v>
       </c>
       <c r="AJ110" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AK110">
         <v>20260812</v>
       </c>
       <c r="AL110" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AP110" t="s">
         <v>165</v>
@@ -18409,19 +18402,19 @@
         <v>2474</v>
       </c>
       <c r="E111" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F111" t="s">
         <v>143</v>
       </c>
       <c r="G111" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="H111" t="s">
         <v>145</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="J111">
         <v>4507425196</v>
@@ -18555,19 +18548,19 @@
         <v>2474</v>
       </c>
       <c r="E112" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F112" t="s">
         <v>143</v>
       </c>
       <c r="G112" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="H112" t="s">
         <v>145</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J112">
         <v>4507488019</v>
@@ -18588,7 +18581,7 @@
         <v>2026</v>
       </c>
       <c r="T112" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V112" t="s">
         <v>205</v>
@@ -18600,7 +18593,7 @@
         <v>152</v>
       </c>
       <c r="Y112" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z112" t="s">
         <v>152</v>
@@ -18707,19 +18700,19 @@
         <v>2474</v>
       </c>
       <c r="E113" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F113" t="s">
         <v>143</v>
       </c>
       <c r="G113" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="H113" t="s">
         <v>145</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J113">
         <v>4507488019</v>
@@ -18740,7 +18733,7 @@
         <v>2026</v>
       </c>
       <c r="T113" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V113" t="s">
         <v>205</v>
@@ -18752,7 +18745,7 @@
         <v>152</v>
       </c>
       <c r="Y113" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z113" t="s">
         <v>152</v>
@@ -18770,7 +18763,7 @@
         <v>20260813</v>
       </c>
       <c r="AH113" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AI113">
         <v>20260813</v>
@@ -18782,7 +18775,7 @@
         <v>20260814</v>
       </c>
       <c r="AL113" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AM113">
         <v>8</v>
@@ -18859,19 +18852,19 @@
         <v>2474</v>
       </c>
       <c r="E114" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F114" t="s">
         <v>143</v>
       </c>
       <c r="G114" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H114" t="s">
         <v>145</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J114">
         <v>4507488019</v>
@@ -18892,7 +18885,7 @@
         <v>2026</v>
       </c>
       <c r="T114" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V114" t="s">
         <v>205</v>
@@ -18904,7 +18897,7 @@
         <v>152</v>
       </c>
       <c r="Y114" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z114" t="s">
         <v>152</v>
@@ -18922,7 +18915,7 @@
         <v>20260813</v>
       </c>
       <c r="AH114" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AI114">
         <v>20260813</v>
@@ -19011,19 +19004,19 @@
         <v>2474</v>
       </c>
       <c r="E115" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F115" t="s">
         <v>143</v>
       </c>
       <c r="G115" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="H115" t="s">
         <v>145</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="J115">
         <v>4507491884</v>
@@ -19044,7 +19037,7 @@
         <v>2026</v>
       </c>
       <c r="T115" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V115" t="s">
         <v>205</v>
@@ -19056,7 +19049,7 @@
         <v>152</v>
       </c>
       <c r="Y115" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z115" t="s">
         <v>152</v>
@@ -19086,7 +19079,7 @@
         <v>20260815</v>
       </c>
       <c r="AL115" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AM115">
         <v>8</v>
@@ -19163,19 +19156,19 @@
         <v>2474</v>
       </c>
       <c r="E116" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F116" t="s">
         <v>143</v>
       </c>
       <c r="G116" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="H116" t="s">
         <v>145</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="J116">
         <v>4507508326</v>
@@ -19196,7 +19189,7 @@
         <v>2026</v>
       </c>
       <c r="T116" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V116" t="s">
         <v>205</v>
@@ -19208,7 +19201,7 @@
         <v>152</v>
       </c>
       <c r="Y116" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z116" t="s">
         <v>152</v>
@@ -19315,19 +19308,19 @@
         <v>2128</v>
       </c>
       <c r="E117" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F117" t="s">
         <v>143</v>
       </c>
       <c r="G117" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H117" t="s">
         <v>145</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J117">
         <v>4507425051</v>
@@ -19348,7 +19341,7 @@
         <v>0</v>
       </c>
       <c r="T117" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V117" t="s">
         <v>205</v>
@@ -19360,7 +19353,7 @@
         <v>152</v>
       </c>
       <c r="Y117" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z117" t="s">
         <v>152</v>
@@ -19413,19 +19406,19 @@
         <v>2128</v>
       </c>
       <c r="E118" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F118" t="s">
         <v>143</v>
       </c>
       <c r="G118" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H118" t="s">
         <v>145</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="J118">
         <v>4507425051</v>
@@ -19446,7 +19439,7 @@
         <v>0</v>
       </c>
       <c r="T118" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V118" t="s">
         <v>205</v>
@@ -19458,7 +19451,7 @@
         <v>152</v>
       </c>
       <c r="Y118" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z118" t="s">
         <v>152</v>
@@ -19511,19 +19504,19 @@
         <v>2128</v>
       </c>
       <c r="E119" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F119" t="s">
         <v>143</v>
       </c>
       <c r="G119" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H119" t="s">
         <v>145</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J119">
         <v>4507425051</v>
@@ -19544,7 +19537,7 @@
         <v>0</v>
       </c>
       <c r="T119" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V119" t="s">
         <v>205</v>
@@ -19556,7 +19549,7 @@
         <v>152</v>
       </c>
       <c r="Y119" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z119" t="s">
         <v>152</v>
@@ -19609,19 +19602,19 @@
         <v>2128</v>
       </c>
       <c r="E120" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F120" t="s">
         <v>143</v>
       </c>
       <c r="G120" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H120" t="s">
         <v>145</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J120">
         <v>4507425051</v>
@@ -19642,7 +19635,7 @@
         <v>0</v>
       </c>
       <c r="T120" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V120" t="s">
         <v>205</v>
@@ -19654,7 +19647,7 @@
         <v>152</v>
       </c>
       <c r="Y120" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z120" t="s">
         <v>152</v>
@@ -19707,19 +19700,19 @@
         <v>2128</v>
       </c>
       <c r="E121" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F121" t="s">
         <v>143</v>
       </c>
       <c r="G121" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="H121" t="s">
         <v>145</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="J121">
         <v>4507425051</v>
@@ -19740,7 +19733,7 @@
         <v>0</v>
       </c>
       <c r="T121" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V121" t="s">
         <v>205</v>
@@ -19752,7 +19745,7 @@
         <v>152</v>
       </c>
       <c r="Y121" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z121" t="s">
         <v>152</v>
@@ -19805,19 +19798,19 @@
         <v>2128</v>
       </c>
       <c r="E122" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F122" t="s">
         <v>143</v>
       </c>
       <c r="G122" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H122" t="s">
         <v>145</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J122">
         <v>4507425051</v>
@@ -19838,7 +19831,7 @@
         <v>0</v>
       </c>
       <c r="T122" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V122" t="s">
         <v>205</v>
@@ -19850,7 +19843,7 @@
         <v>152</v>
       </c>
       <c r="Y122" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z122" t="s">
         <v>152</v>
@@ -19903,19 +19896,19 @@
         <v>2128</v>
       </c>
       <c r="E123" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F123" t="s">
         <v>143</v>
       </c>
       <c r="G123" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H123" t="s">
         <v>145</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J123">
         <v>4507425051</v>
@@ -19936,7 +19929,7 @@
         <v>0</v>
       </c>
       <c r="T123" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V123" t="s">
         <v>205</v>
@@ -19948,7 +19941,7 @@
         <v>152</v>
       </c>
       <c r="Y123" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z123" t="s">
         <v>152</v>
@@ -20001,19 +19994,19 @@
         <v>2128</v>
       </c>
       <c r="E124" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F124" t="s">
         <v>143</v>
       </c>
       <c r="G124" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H124" t="s">
         <v>145</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J124">
         <v>4507425051</v>
@@ -20034,7 +20027,7 @@
         <v>0</v>
       </c>
       <c r="T124" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V124" t="s">
         <v>205</v>
@@ -20046,7 +20039,7 @@
         <v>152</v>
       </c>
       <c r="Y124" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z124" t="s">
         <v>152</v>
@@ -20099,19 +20092,19 @@
         <v>2128</v>
       </c>
       <c r="E125" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F125" t="s">
         <v>143</v>
       </c>
       <c r="G125" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="H125" t="s">
         <v>145</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J125">
         <v>4507425051</v>
@@ -20132,7 +20125,7 @@
         <v>0</v>
       </c>
       <c r="T125" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V125" t="s">
         <v>205</v>
@@ -20144,7 +20137,7 @@
         <v>152</v>
       </c>
       <c r="Y125" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z125" t="s">
         <v>152</v>
@@ -20197,19 +20190,19 @@
         <v>2128</v>
       </c>
       <c r="E126" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F126" t="s">
         <v>143</v>
       </c>
       <c r="G126" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H126" t="s">
         <v>145</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J126">
         <v>4507425051</v>
@@ -20230,7 +20223,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V126" t="s">
         <v>205</v>
@@ -20242,7 +20235,7 @@
         <v>152</v>
       </c>
       <c r="Y126" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z126" t="s">
         <v>152</v>
@@ -20295,19 +20288,19 @@
         <v>2128</v>
       </c>
       <c r="E127" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F127" t="s">
         <v>143</v>
       </c>
       <c r="G127" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="H127" t="s">
         <v>145</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J127">
         <v>4507425051</v>
@@ -20328,7 +20321,7 @@
         <v>0</v>
       </c>
       <c r="T127" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V127" t="s">
         <v>205</v>
@@ -20340,7 +20333,7 @@
         <v>152</v>
       </c>
       <c r="Y127" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z127" t="s">
         <v>152</v>
@@ -20393,19 +20386,19 @@
         <v>2128</v>
       </c>
       <c r="E128" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F128" t="s">
         <v>143</v>
       </c>
       <c r="G128" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H128" t="s">
         <v>145</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J128">
         <v>4507425051</v>
@@ -20426,7 +20419,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V128" t="s">
         <v>205</v>
@@ -20438,7 +20431,7 @@
         <v>152</v>
       </c>
       <c r="Y128" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z128" t="s">
         <v>152</v>
@@ -20491,25 +20484,25 @@
         <v>2128</v>
       </c>
       <c r="E129" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F129" t="s">
         <v>143</v>
       </c>
       <c r="G129" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H129" t="s">
         <v>145</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J129">
         <v>4507425051</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="O129">
         <v>2000009157</v>
@@ -20524,7 +20517,7 @@
         <v>0</v>
       </c>
       <c r="T129" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V129" t="s">
         <v>205</v>
@@ -20536,7 +20529,7 @@
         <v>152</v>
       </c>
       <c r="Y129" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z129" t="s">
         <v>152</v>
@@ -20589,25 +20582,25 @@
         <v>2128</v>
       </c>
       <c r="E130" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F130" t="s">
         <v>143</v>
       </c>
       <c r="G130" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H130" t="s">
         <v>145</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J130">
         <v>4507425051</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O130">
         <v>2000009157</v>
@@ -20622,7 +20615,7 @@
         <v>0</v>
       </c>
       <c r="T130" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V130" t="s">
         <v>205</v>
@@ -20634,7 +20627,7 @@
         <v>152</v>
       </c>
       <c r="Y130" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z130" t="s">
         <v>152</v>
@@ -20687,19 +20680,19 @@
         <v>2128</v>
       </c>
       <c r="E131" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F131" t="s">
         <v>143</v>
       </c>
       <c r="G131" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H131" t="s">
         <v>145</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J131">
         <v>4507425051</v>
@@ -20720,7 +20713,7 @@
         <v>0</v>
       </c>
       <c r="T131" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V131" t="s">
         <v>205</v>
@@ -20732,7 +20725,7 @@
         <v>152</v>
       </c>
       <c r="Y131" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z131" t="s">
         <v>152</v>
@@ -20785,19 +20778,19 @@
         <v>2128</v>
       </c>
       <c r="E132" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F132" t="s">
         <v>143</v>
       </c>
       <c r="G132" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H132" t="s">
         <v>145</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J132">
         <v>4507439331</v>
@@ -20883,19 +20876,19 @@
         <v>2128</v>
       </c>
       <c r="E133" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F133" t="s">
         <v>143</v>
       </c>
       <c r="G133" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H133" t="s">
         <v>145</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J133">
         <v>4507439331</v>
@@ -20981,19 +20974,19 @@
         <v>2128</v>
       </c>
       <c r="E134" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F134" t="s">
         <v>143</v>
       </c>
       <c r="G134" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H134" t="s">
         <v>145</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J134">
         <v>4507439331</v>
@@ -21079,19 +21072,19 @@
         <v>2128</v>
       </c>
       <c r="E135" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F135" t="s">
         <v>143</v>
       </c>
       <c r="G135" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H135" t="s">
         <v>145</v>
       </c>
       <c r="I135" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J135">
         <v>4507439331</v>
@@ -21177,19 +21170,19 @@
         <v>2128</v>
       </c>
       <c r="E136" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F136" t="s">
         <v>143</v>
       </c>
       <c r="G136" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H136" t="s">
         <v>145</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J136">
         <v>4507439331</v>
@@ -21275,19 +21268,19 @@
         <v>2128</v>
       </c>
       <c r="E137" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F137" t="s">
         <v>143</v>
       </c>
       <c r="G137" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H137" t="s">
         <v>145</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J137">
         <v>4507439331</v>
@@ -21373,19 +21366,19 @@
         <v>2128</v>
       </c>
       <c r="E138" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F138" t="s">
         <v>143</v>
       </c>
       <c r="G138" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H138" t="s">
         <v>145</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="J138">
         <v>4507439331</v>
@@ -21424,7 +21417,7 @@
         <v>152</v>
       </c>
       <c r="AA138" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="AF138" t="s">
         <v>153</v>
@@ -21439,13 +21432,13 @@
         <v>20260814</v>
       </c>
       <c r="AJ138" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="AK138">
         <v>20260814</v>
       </c>
       <c r="AL138" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="AP138" t="s">
         <v>165</v>
@@ -21516,25 +21509,25 @@
         <v>2128</v>
       </c>
       <c r="E139" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F139" t="s">
         <v>143</v>
       </c>
       <c r="G139" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H139" t="s">
         <v>145</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J139">
         <v>4507439331</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="O139">
         <v>2000008826</v>
@@ -21614,25 +21607,25 @@
         <v>2128</v>
       </c>
       <c r="E140" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F140" t="s">
         <v>143</v>
       </c>
       <c r="G140" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H140" t="s">
         <v>145</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J140">
         <v>4507439331</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O140">
         <v>2000008826</v>
@@ -21712,19 +21705,19 @@
         <v>2128</v>
       </c>
       <c r="E141" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F141" t="s">
         <v>143</v>
       </c>
       <c r="G141" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H141" t="s">
         <v>145</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="J141">
         <v>4507493285</v>
@@ -21745,7 +21738,7 @@
         <v>0</v>
       </c>
       <c r="T141" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V141" t="s">
         <v>205</v>
@@ -21757,7 +21750,7 @@
         <v>152</v>
       </c>
       <c r="Y141" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z141" t="s">
         <v>152</v>
@@ -21819,19 +21812,19 @@
         <v>2128</v>
       </c>
       <c r="E142" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F142" t="s">
         <v>143</v>
       </c>
       <c r="G142" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H142" t="s">
         <v>145</v>
       </c>
       <c r="I142" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J142">
         <v>4507493285</v>
@@ -21852,7 +21845,7 @@
         <v>0</v>
       </c>
       <c r="T142" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V142" t="s">
         <v>205</v>
@@ -21864,7 +21857,7 @@
         <v>152</v>
       </c>
       <c r="Y142" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z142" t="s">
         <v>152</v>
@@ -21926,19 +21919,19 @@
         <v>2128</v>
       </c>
       <c r="E143" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F143" t="s">
         <v>143</v>
       </c>
       <c r="G143" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H143" t="s">
         <v>145</v>
       </c>
       <c r="I143" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J143">
         <v>4507493285</v>
@@ -21959,7 +21952,7 @@
         <v>0</v>
       </c>
       <c r="T143" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V143" t="s">
         <v>205</v>
@@ -21971,7 +21964,7 @@
         <v>152</v>
       </c>
       <c r="Y143" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z143" t="s">
         <v>152</v>
@@ -22033,19 +22026,19 @@
         <v>2128</v>
       </c>
       <c r="E144" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F144" t="s">
         <v>143</v>
       </c>
       <c r="G144" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H144" t="s">
         <v>145</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J144">
         <v>4507439331</v>
@@ -22084,7 +22077,7 @@
         <v>152</v>
       </c>
       <c r="AA144" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AE144">
         <v>20260811</v>
@@ -22179,19 +22172,19 @@
         <v>2128</v>
       </c>
       <c r="E145" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F145" t="s">
         <v>143</v>
       </c>
       <c r="G145" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H145" t="s">
         <v>145</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J145">
         <v>4507439331</v>
@@ -22230,7 +22223,7 @@
         <v>152</v>
       </c>
       <c r="AA145" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AE145">
         <v>20260811</v>
@@ -22325,19 +22318,19 @@
         <v>2128</v>
       </c>
       <c r="E146" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F146" t="s">
         <v>143</v>
       </c>
       <c r="G146" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H146" t="s">
         <v>145</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J146">
         <v>4507439331</v>
@@ -22376,7 +22369,7 @@
         <v>152</v>
       </c>
       <c r="AA146" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AE146">
         <v>20260811</v>
@@ -22471,19 +22464,19 @@
         <v>2128</v>
       </c>
       <c r="E147" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F147" t="s">
         <v>143</v>
       </c>
       <c r="G147" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H147" t="s">
         <v>145</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="J147">
         <v>4507439331</v>
@@ -22522,7 +22515,7 @@
         <v>152</v>
       </c>
       <c r="AA147" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="AE147">
         <v>20260812</v>
@@ -22617,19 +22610,19 @@
         <v>2128</v>
       </c>
       <c r="E148" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F148" t="s">
         <v>143</v>
       </c>
       <c r="G148" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H148" t="s">
         <v>145</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="J148">
         <v>4507439331</v>
@@ -22668,7 +22661,7 @@
         <v>152</v>
       </c>
       <c r="AA148" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AE148">
         <v>20260812</v>
@@ -22763,19 +22756,19 @@
         <v>2128</v>
       </c>
       <c r="E149" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F149" t="s">
         <v>143</v>
       </c>
       <c r="G149" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="H149" t="s">
         <v>145</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="J149">
         <v>4507439331</v>
@@ -22909,19 +22902,19 @@
         <v>2128</v>
       </c>
       <c r="E150" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F150" t="s">
         <v>143</v>
       </c>
       <c r="G150" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H150" t="s">
         <v>145</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="J150">
         <v>4507493285</v>
@@ -22942,7 +22935,7 @@
         <v>2026</v>
       </c>
       <c r="T150" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V150" t="s">
         <v>205</v>
@@ -22954,7 +22947,7 @@
         <v>152</v>
       </c>
       <c r="Y150" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z150" t="s">
         <v>152</v>
@@ -23061,19 +23054,19 @@
         <v>2108</v>
       </c>
       <c r="E151" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F151" t="s">
         <v>249</v>
       </c>
       <c r="G151" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="H151" t="s">
         <v>145</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J151">
         <v>4507508738</v>
@@ -23180,19 +23173,19 @@
         <v>2108</v>
       </c>
       <c r="E152" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F152" t="s">
         <v>249</v>
       </c>
       <c r="G152" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="H152" t="s">
         <v>145</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J152">
         <v>4507508738</v>
@@ -23302,19 +23295,19 @@
         <v>2108</v>
       </c>
       <c r="E153" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F153" t="s">
         <v>249</v>
       </c>
       <c r="G153" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="H153" t="s">
         <v>145</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="J153">
         <v>4507508738</v>
@@ -23421,19 +23414,19 @@
         <v>2108</v>
       </c>
       <c r="E154" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F154" t="s">
         <v>249</v>
       </c>
       <c r="G154" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="H154" t="s">
         <v>145</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="J154">
         <v>4507508738</v>
@@ -23540,19 +23533,19 @@
         <v>2108</v>
       </c>
       <c r="E155" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F155" t="s">
         <v>249</v>
       </c>
       <c r="G155" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H155" t="s">
         <v>145</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="J155">
         <v>4507508738</v>
@@ -23659,19 +23652,19 @@
         <v>2108</v>
       </c>
       <c r="E156" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F156" t="s">
         <v>249</v>
       </c>
       <c r="G156" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="H156" t="s">
         <v>145</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="J156">
         <v>4507508738</v>
@@ -23778,19 +23771,19 @@
         <v>2108</v>
       </c>
       <c r="E157" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F157" t="s">
         <v>249</v>
       </c>
       <c r="G157" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="H157" t="s">
         <v>145</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="J157">
         <v>4507508738</v>
@@ -23897,19 +23890,19 @@
         <v>2108</v>
       </c>
       <c r="E158" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F158" t="s">
         <v>249</v>
       </c>
       <c r="G158" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="H158" t="s">
         <v>145</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="J158">
         <v>4507508738</v>
@@ -24016,19 +24009,19 @@
         <v>2108</v>
       </c>
       <c r="E159" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F159" t="s">
         <v>249</v>
       </c>
       <c r="G159" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="H159" t="s">
         <v>145</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J159">
         <v>4507508738</v>
@@ -24135,19 +24128,19 @@
         <v>2108</v>
       </c>
       <c r="E160" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F160" t="s">
         <v>249</v>
       </c>
       <c r="G160" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="H160" t="s">
         <v>145</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="J160">
         <v>4507508738</v>
@@ -24254,19 +24247,19 @@
         <v>2108</v>
       </c>
       <c r="E161" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F161" t="s">
         <v>249</v>
       </c>
       <c r="G161" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="H161" t="s">
         <v>145</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="J161">
         <v>4507508738</v>
@@ -24370,19 +24363,19 @@
         <v>2108</v>
       </c>
       <c r="E162" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="F162" t="s">
         <v>249</v>
       </c>
       <c r="G162" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="H162" t="s">
         <v>145</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="J162">
         <v>4507471133</v>
@@ -24403,7 +24396,7 @@
         <v>2026</v>
       </c>
       <c r="T162" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V162" t="s">
         <v>205</v>
@@ -24415,7 +24408,7 @@
         <v>152</v>
       </c>
       <c r="Y162" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z162" t="s">
         <v>152</v>
@@ -24445,7 +24438,7 @@
         <v>20260812</v>
       </c>
       <c r="AL162" s="1" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="AM162">
         <v>8</v>
@@ -24531,19 +24524,19 @@
         <v>2109</v>
       </c>
       <c r="E163" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F163" t="s">
         <v>249</v>
       </c>
       <c r="G163" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H163" t="s">
         <v>145</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J163">
         <v>4507420978</v>
@@ -24564,7 +24557,7 @@
         <v>0</v>
       </c>
       <c r="T163" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V163" t="s">
         <v>205</v>
@@ -24576,7 +24569,7 @@
         <v>152</v>
       </c>
       <c r="Y163" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z163" t="s">
         <v>152</v>
@@ -24591,13 +24584,13 @@
         <v>20260814</v>
       </c>
       <c r="AH163" s="1" t="s">
-        <v>443</v>
+        <v>595</v>
       </c>
       <c r="AI163">
         <v>20260814</v>
       </c>
       <c r="AJ163" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AK163">
         <v>20260814</v>
@@ -24689,19 +24682,19 @@
         <v>2109</v>
       </c>
       <c r="E164" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F164" t="s">
         <v>249</v>
       </c>
       <c r="G164" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="H164" t="s">
         <v>145</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="J164">
         <v>4507420978</v>
@@ -24722,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="T164" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V164" t="s">
         <v>205</v>
@@ -24734,7 +24727,7 @@
         <v>152</v>
       </c>
       <c r="Y164" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z164" t="s">
         <v>152</v>
@@ -24847,19 +24840,19 @@
         <v>2109</v>
       </c>
       <c r="E165" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F165" t="s">
         <v>249</v>
       </c>
       <c r="G165" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="H165" t="s">
         <v>145</v>
       </c>
       <c r="I165" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="J165">
         <v>4507420978</v>
@@ -24880,7 +24873,7 @@
         <v>0</v>
       </c>
       <c r="T165" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V165" t="s">
         <v>205</v>
@@ -24892,7 +24885,7 @@
         <v>152</v>
       </c>
       <c r="Y165" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z165" t="s">
         <v>152</v>
@@ -24919,7 +24912,7 @@
         <v>20260815</v>
       </c>
       <c r="AL165" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AM165">
         <v>8</v>
@@ -25005,25 +24998,25 @@
         <v>2109</v>
       </c>
       <c r="E166" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F166" t="s">
         <v>249</v>
       </c>
       <c r="G166" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H166" t="s">
         <v>145</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="J166">
         <v>4507420978</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="O166">
         <v>2000009157</v>
@@ -25038,7 +25031,7 @@
         <v>0</v>
       </c>
       <c r="T166" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V166" t="s">
         <v>205</v>
@@ -25050,7 +25043,7 @@
         <v>152</v>
       </c>
       <c r="Y166" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z166" t="s">
         <v>152</v>
@@ -25077,7 +25070,7 @@
         <v>20260815</v>
       </c>
       <c r="AL166" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AM166">
         <v>8</v>
@@ -25163,19 +25156,19 @@
         <v>2109</v>
       </c>
       <c r="E167" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F167" t="s">
         <v>249</v>
       </c>
       <c r="G167" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H167" t="s">
         <v>145</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="J167">
         <v>4507420978</v>
@@ -25196,7 +25189,7 @@
         <v>0</v>
       </c>
       <c r="T167" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V167" t="s">
         <v>205</v>
@@ -25208,7 +25201,7 @@
         <v>152</v>
       </c>
       <c r="Y167" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z167" t="s">
         <v>152</v>
@@ -25279,25 +25272,25 @@
         <v>2109</v>
       </c>
       <c r="E168" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F168" t="s">
         <v>249</v>
       </c>
       <c r="G168" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H168" t="s">
         <v>145</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="J168">
         <v>4507420978</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="O168">
         <v>2000009157</v>
@@ -25312,7 +25305,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V168" t="s">
         <v>205</v>
@@ -25324,7 +25317,7 @@
         <v>152</v>
       </c>
       <c r="Y168" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z168" t="s">
         <v>152</v>
@@ -25398,25 +25391,25 @@
         <v>2109</v>
       </c>
       <c r="E169" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F169" t="s">
         <v>249</v>
       </c>
       <c r="G169" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H169" t="s">
         <v>145</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J169">
         <v>4507420978</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="O169">
         <v>2000009157</v>
@@ -25431,7 +25424,7 @@
         <v>0</v>
       </c>
       <c r="T169" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V169" t="s">
         <v>205</v>
@@ -25443,7 +25436,7 @@
         <v>152</v>
       </c>
       <c r="Y169" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z169" t="s">
         <v>152</v>
@@ -25517,25 +25510,25 @@
         <v>2109</v>
       </c>
       <c r="E170" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F170" t="s">
         <v>249</v>
       </c>
       <c r="G170" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H170" t="s">
         <v>145</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="J170">
         <v>4507420978</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="O170">
         <v>2000009157</v>
@@ -25550,7 +25543,7 @@
         <v>0</v>
       </c>
       <c r="T170" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V170" t="s">
         <v>205</v>
@@ -25562,7 +25555,7 @@
         <v>152</v>
       </c>
       <c r="Y170" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z170" t="s">
         <v>152</v>
@@ -25636,25 +25629,25 @@
         <v>2109</v>
       </c>
       <c r="E171" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F171" t="s">
         <v>249</v>
       </c>
       <c r="G171" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="H171" t="s">
         <v>145</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="J171">
         <v>4507420978</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="O171">
         <v>2000009157</v>
@@ -25669,7 +25662,7 @@
         <v>0</v>
       </c>
       <c r="T171" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V171" t="s">
         <v>205</v>
@@ -25681,7 +25674,7 @@
         <v>152</v>
       </c>
       <c r="Y171" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z171" t="s">
         <v>152</v>
@@ -25755,19 +25748,19 @@
         <v>2109</v>
       </c>
       <c r="E172" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F172" t="s">
         <v>249</v>
       </c>
       <c r="G172" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H172" t="s">
         <v>145</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="J172">
         <v>4507420978</v>
@@ -25788,7 +25781,7 @@
         <v>2026</v>
       </c>
       <c r="T172" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V172" t="s">
         <v>205</v>
@@ -25800,7 +25793,7 @@
         <v>152</v>
       </c>
       <c r="Y172" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z172" t="s">
         <v>152</v>
@@ -25824,7 +25817,7 @@
         <v>20260813</v>
       </c>
       <c r="AJ172" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AK172">
         <v>20260813</v>
@@ -25916,19 +25909,19 @@
         <v>2109</v>
       </c>
       <c r="E173" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F173" t="s">
         <v>249</v>
       </c>
       <c r="G173" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="H173" t="s">
         <v>145</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="J173">
         <v>4507420978</v>
@@ -25949,7 +25942,7 @@
         <v>2026</v>
       </c>
       <c r="T173" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V173" t="s">
         <v>205</v>
@@ -25961,7 +25954,7 @@
         <v>152</v>
       </c>
       <c r="Y173" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z173" t="s">
         <v>152</v>
@@ -25985,13 +25978,13 @@
         <v>20260813</v>
       </c>
       <c r="AJ173" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AK173">
         <v>20260813</v>
       </c>
       <c r="AL173" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AM173">
         <v>8</v>
@@ -26077,19 +26070,19 @@
         <v>2109</v>
       </c>
       <c r="E174" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F174" t="s">
         <v>249</v>
       </c>
       <c r="G174" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H174" t="s">
         <v>145</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="J174">
         <v>4507420978</v>
@@ -26110,7 +26103,7 @@
         <v>2026</v>
       </c>
       <c r="T174" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V174" t="s">
         <v>205</v>
@@ -26122,7 +26115,7 @@
         <v>152</v>
       </c>
       <c r="Y174" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z174" t="s">
         <v>152</v>
@@ -26146,7 +26139,7 @@
         <v>20260813</v>
       </c>
       <c r="AJ174" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AK174">
         <v>20260813</v>
@@ -26238,19 +26231,19 @@
         <v>2109</v>
       </c>
       <c r="E175" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F175" t="s">
         <v>249</v>
       </c>
       <c r="G175" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="H175" t="s">
         <v>145</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="J175">
         <v>4507420978</v>
@@ -26271,7 +26264,7 @@
         <v>2026</v>
       </c>
       <c r="T175" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V175" t="s">
         <v>205</v>
@@ -26283,7 +26276,7 @@
         <v>152</v>
       </c>
       <c r="Y175" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z175" t="s">
         <v>152</v>
@@ -26301,13 +26294,13 @@
         <v>20260813</v>
       </c>
       <c r="AH175" s="1" t="s">
-        <v>443</v>
+        <v>595</v>
       </c>
       <c r="AI175">
         <v>20260813</v>
       </c>
       <c r="AJ175" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AK175">
         <v>20260813</v>
@@ -26399,19 +26392,19 @@
         <v>2109</v>
       </c>
       <c r="E176" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F176" t="s">
         <v>249</v>
       </c>
       <c r="G176" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="H176" t="s">
         <v>145</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="J176">
         <v>4507420978</v>
@@ -26432,7 +26425,7 @@
         <v>2026</v>
       </c>
       <c r="T176" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V176" t="s">
         <v>205</v>
@@ -26444,7 +26437,7 @@
         <v>152</v>
       </c>
       <c r="Y176" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z176" t="s">
         <v>152</v>
@@ -26560,19 +26553,19 @@
         <v>2109</v>
       </c>
       <c r="E177" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F177" t="s">
         <v>249</v>
       </c>
       <c r="G177" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H177" t="s">
         <v>145</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="J177">
         <v>4507420978</v>
@@ -26593,7 +26586,7 @@
         <v>2026</v>
       </c>
       <c r="T177" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V177" t="s">
         <v>205</v>
@@ -26605,7 +26598,7 @@
         <v>152</v>
       </c>
       <c r="Y177" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z177" t="s">
         <v>152</v>
@@ -26721,19 +26714,19 @@
         <v>2109</v>
       </c>
       <c r="E178" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F178" t="s">
         <v>249</v>
       </c>
       <c r="G178" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H178" t="s">
         <v>145</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="J178">
         <v>4507420978</v>
@@ -26754,7 +26747,7 @@
         <v>2026</v>
       </c>
       <c r="T178" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V178" t="s">
         <v>205</v>
@@ -26766,7 +26759,7 @@
         <v>152</v>
       </c>
       <c r="Y178" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z178" t="s">
         <v>152</v>
@@ -26882,19 +26875,19 @@
         <v>2109</v>
       </c>
       <c r="E179" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F179" t="s">
         <v>249</v>
       </c>
       <c r="G179" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H179" t="s">
         <v>145</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="J179">
         <v>4507420978</v>
@@ -26915,7 +26908,7 @@
         <v>2026</v>
       </c>
       <c r="T179" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V179" t="s">
         <v>205</v>
@@ -26927,7 +26920,7 @@
         <v>152</v>
       </c>
       <c r="Y179" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z179" t="s">
         <v>152</v>
@@ -27043,19 +27036,19 @@
         <v>2109</v>
       </c>
       <c r="E180" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F180" t="s">
         <v>249</v>
       </c>
       <c r="G180" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H180" t="s">
         <v>145</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="J180">
         <v>4507420978</v>
@@ -27076,7 +27069,7 @@
         <v>2026</v>
       </c>
       <c r="T180" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V180" t="s">
         <v>205</v>
@@ -27088,7 +27081,7 @@
         <v>152</v>
       </c>
       <c r="Y180" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z180" t="s">
         <v>152</v>
@@ -27204,19 +27197,19 @@
         <v>2109</v>
       </c>
       <c r="E181" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F181" t="s">
         <v>249</v>
       </c>
       <c r="G181" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H181" t="s">
         <v>145</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="J181">
         <v>4507420978</v>
@@ -27237,7 +27230,7 @@
         <v>2026</v>
       </c>
       <c r="T181" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V181" t="s">
         <v>205</v>
@@ -27249,7 +27242,7 @@
         <v>152</v>
       </c>
       <c r="Y181" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z181" t="s">
         <v>152</v>
@@ -27365,19 +27358,19 @@
         <v>2109</v>
       </c>
       <c r="E182" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F182" t="s">
         <v>249</v>
       </c>
       <c r="G182" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="H182" t="s">
         <v>145</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="J182">
         <v>4507420978</v>
@@ -27398,7 +27391,7 @@
         <v>2026</v>
       </c>
       <c r="T182" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V182" t="s">
         <v>205</v>
@@ -27410,7 +27403,7 @@
         <v>152</v>
       </c>
       <c r="Y182" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z182" t="s">
         <v>152</v>
@@ -27440,7 +27433,7 @@
         <v>20260814</v>
       </c>
       <c r="AL182" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AM182">
         <v>8</v>
@@ -27526,19 +27519,19 @@
         <v>2109</v>
       </c>
       <c r="E183" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F183" t="s">
         <v>249</v>
       </c>
       <c r="G183" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H183" t="s">
         <v>145</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="J183">
         <v>4507420978</v>
@@ -27559,7 +27552,7 @@
         <v>2026</v>
       </c>
       <c r="T183" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V183" t="s">
         <v>205</v>
@@ -27571,7 +27564,7 @@
         <v>152</v>
       </c>
       <c r="Y183" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z183" t="s">
         <v>152</v>
@@ -27595,13 +27588,13 @@
         <v>20260814</v>
       </c>
       <c r="AJ183" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AK183">
         <v>20260814</v>
       </c>
       <c r="AL183" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AM183">
         <v>8</v>
@@ -27687,19 +27680,19 @@
         <v>2109</v>
       </c>
       <c r="E184" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F184" t="s">
         <v>249</v>
       </c>
       <c r="G184" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H184" t="s">
         <v>145</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J184">
         <v>4507420978</v>
@@ -27720,7 +27713,7 @@
         <v>2026</v>
       </c>
       <c r="T184" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V184" t="s">
         <v>205</v>
@@ -27732,7 +27725,7 @@
         <v>152</v>
       </c>
       <c r="Y184" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z184" t="s">
         <v>152</v>
@@ -27756,7 +27749,7 @@
         <v>20260814</v>
       </c>
       <c r="AJ184" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AK184">
         <v>20260814</v>
@@ -27848,19 +27841,19 @@
         <v>2109</v>
       </c>
       <c r="E185" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F185" t="s">
         <v>249</v>
       </c>
       <c r="G185" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H185" t="s">
         <v>145</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="J185">
         <v>4507420978</v>
@@ -27881,7 +27874,7 @@
         <v>2026</v>
       </c>
       <c r="T185" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V185" t="s">
         <v>205</v>
@@ -27893,7 +27886,7 @@
         <v>152</v>
       </c>
       <c r="Y185" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z185" t="s">
         <v>152</v>
@@ -28009,19 +28002,19 @@
         <v>2109</v>
       </c>
       <c r="E186" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F186" t="s">
         <v>249</v>
       </c>
       <c r="G186" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="H186" t="s">
         <v>145</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J186">
         <v>4507420978</v>
@@ -28042,7 +28035,7 @@
         <v>2026</v>
       </c>
       <c r="T186" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V186" t="s">
         <v>205</v>
@@ -28054,7 +28047,7 @@
         <v>152</v>
       </c>
       <c r="Y186" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z186" t="s">
         <v>152</v>
@@ -28170,19 +28163,19 @@
         <v>2109</v>
       </c>
       <c r="E187" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F187" t="s">
         <v>249</v>
       </c>
       <c r="G187" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="H187" t="s">
         <v>145</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="J187">
         <v>4507420978</v>
@@ -28203,7 +28196,7 @@
         <v>2026</v>
       </c>
       <c r="T187" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V187" t="s">
         <v>205</v>
@@ -28215,7 +28208,7 @@
         <v>152</v>
       </c>
       <c r="Y187" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z187" t="s">
         <v>152</v>
@@ -28331,25 +28324,25 @@
         <v>2109</v>
       </c>
       <c r="E188" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F188" t="s">
         <v>249</v>
       </c>
       <c r="G188" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H188" t="s">
         <v>145</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="J188">
         <v>4507420978</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O188">
         <v>2000009157</v>
@@ -28364,7 +28357,7 @@
         <v>2026</v>
       </c>
       <c r="T188" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V188" t="s">
         <v>205</v>
@@ -28376,7 +28369,7 @@
         <v>152</v>
       </c>
       <c r="Y188" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z188" t="s">
         <v>152</v>
@@ -28400,13 +28393,13 @@
         <v>20260815</v>
       </c>
       <c r="AJ188" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AK188">
         <v>20260815</v>
       </c>
       <c r="AL188" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AM188">
         <v>8</v>
@@ -28492,19 +28485,19 @@
         <v>2109</v>
       </c>
       <c r="E189" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F189" t="s">
         <v>249</v>
       </c>
       <c r="G189" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H189" t="s">
         <v>145</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="J189">
         <v>4507420978</v>
@@ -28525,7 +28518,7 @@
         <v>2026</v>
       </c>
       <c r="T189" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V189" t="s">
         <v>205</v>
@@ -28537,7 +28530,7 @@
         <v>152</v>
       </c>
       <c r="Y189" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z189" t="s">
         <v>152</v>
@@ -28561,7 +28554,7 @@
         <v>20260815</v>
       </c>
       <c r="AJ189" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AK189">
         <v>20260815</v>
@@ -28653,19 +28646,19 @@
         <v>2109</v>
       </c>
       <c r="E190" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F190" t="s">
         <v>249</v>
       </c>
       <c r="G190" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="H190" t="s">
         <v>145</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="J190">
         <v>4507420978</v>
@@ -28686,7 +28679,7 @@
         <v>2026</v>
       </c>
       <c r="T190" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V190" t="s">
         <v>205</v>
@@ -28698,7 +28691,7 @@
         <v>152</v>
       </c>
       <c r="Y190" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z190" t="s">
         <v>152</v>
@@ -28716,7 +28709,7 @@
         <v>20260815</v>
       </c>
       <c r="AH190" s="1" t="s">
-        <v>443</v>
+        <v>595</v>
       </c>
       <c r="AI190">
         <v>20260815</v>
@@ -28814,25 +28807,25 @@
         <v>2109</v>
       </c>
       <c r="E191" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F191" t="s">
         <v>249</v>
       </c>
       <c r="G191" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H191" t="s">
         <v>145</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="J191">
         <v>4507420978</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="O191">
         <v>2000009157</v>
@@ -28847,7 +28840,7 @@
         <v>2026</v>
       </c>
       <c r="T191" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V191" t="s">
         <v>205</v>
@@ -28859,7 +28852,7 @@
         <v>152</v>
       </c>
       <c r="Y191" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z191" t="s">
         <v>152</v>
@@ -28975,25 +28968,25 @@
         <v>2109</v>
       </c>
       <c r="E192" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F192" t="s">
         <v>249</v>
       </c>
       <c r="G192" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H192" t="s">
         <v>145</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J192">
         <v>4507420978</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="O192">
         <v>2000009157</v>
@@ -29008,7 +29001,7 @@
         <v>2026</v>
       </c>
       <c r="T192" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V192" t="s">
         <v>205</v>
@@ -29020,7 +29013,7 @@
         <v>152</v>
       </c>
       <c r="Y192" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z192" t="s">
         <v>152</v>
@@ -29044,7 +29037,7 @@
         <v>20260815</v>
       </c>
       <c r="AJ192" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AK192">
         <v>20260815</v>
@@ -29136,19 +29129,19 @@
         <v>2109</v>
       </c>
       <c r="E193" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F193" t="s">
         <v>249</v>
       </c>
       <c r="G193" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H193" t="s">
         <v>145</v>
       </c>
       <c r="I193" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J193">
         <v>4507443671</v>
@@ -29169,7 +29162,7 @@
         <v>2026</v>
       </c>
       <c r="T193" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V193" t="s">
         <v>205</v>
@@ -29181,7 +29174,7 @@
         <v>152</v>
       </c>
       <c r="Y193" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z193" t="s">
         <v>152</v>
@@ -29199,7 +29192,7 @@
         <v>20260811</v>
       </c>
       <c r="AH193" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AI193">
         <v>20260810</v>
@@ -29211,7 +29204,7 @@
         <v>20260811</v>
       </c>
       <c r="AL193" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AP193" t="s">
         <v>165</v>
@@ -29291,19 +29284,19 @@
         <v>2109</v>
       </c>
       <c r="E194" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F194" t="s">
         <v>249</v>
       </c>
       <c r="G194" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H194" t="s">
         <v>145</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="J194">
         <v>4507443671</v>
@@ -29324,7 +29317,7 @@
         <v>2026</v>
       </c>
       <c r="T194" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V194" t="s">
         <v>205</v>
@@ -29336,7 +29329,7 @@
         <v>152</v>
       </c>
       <c r="Y194" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z194" t="s">
         <v>152</v>
@@ -29354,13 +29347,13 @@
         <v>20260811</v>
       </c>
       <c r="AH194" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AI194">
         <v>20260811</v>
       </c>
       <c r="AJ194" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="AK194">
         <v>20260811</v>
@@ -29452,19 +29445,19 @@
         <v>2109</v>
       </c>
       <c r="E195" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F195" t="s">
         <v>249</v>
       </c>
       <c r="G195" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H195" t="s">
         <v>145</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J195">
         <v>4507443671</v>
@@ -29485,7 +29478,7 @@
         <v>2026</v>
       </c>
       <c r="T195" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V195" t="s">
         <v>205</v>
@@ -29497,7 +29490,7 @@
         <v>152</v>
       </c>
       <c r="Y195" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z195" t="s">
         <v>152</v>
@@ -29527,7 +29520,7 @@
         <v>20260812</v>
       </c>
       <c r="AL195" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="AM195">
         <v>8</v>
@@ -29613,19 +29606,19 @@
         <v>2109</v>
       </c>
       <c r="E196" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F196" t="s">
         <v>249</v>
       </c>
       <c r="G196" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H196" t="s">
         <v>145</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="J196">
         <v>4507443671</v>
@@ -29646,7 +29639,7 @@
         <v>2026</v>
       </c>
       <c r="T196" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V196" t="s">
         <v>205</v>
@@ -29658,7 +29651,7 @@
         <v>152</v>
       </c>
       <c r="Y196" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z196" t="s">
         <v>152</v>
@@ -29774,19 +29767,19 @@
         <v>2109</v>
       </c>
       <c r="E197" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F197" t="s">
         <v>249</v>
       </c>
       <c r="G197" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H197" t="s">
         <v>145</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="J197">
         <v>4507469608</v>
@@ -29843,13 +29836,13 @@
         <v>20260812</v>
       </c>
       <c r="AJ197" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="AK197">
         <v>20260812</v>
       </c>
       <c r="AL197" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AM197">
         <v>8102026</v>
@@ -29938,19 +29931,19 @@
         <v>2109</v>
       </c>
       <c r="E198" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F198" t="s">
         <v>249</v>
       </c>
       <c r="G198" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H198" t="s">
         <v>145</v>
       </c>
       <c r="I198" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="J198">
         <v>4507469608</v>
@@ -30007,13 +30000,13 @@
         <v>20260812</v>
       </c>
       <c r="AJ198" s="1" t="s">
-        <v>342</v>
+        <v>693</v>
       </c>
       <c r="AK198">
         <v>20260812</v>
       </c>
       <c r="AL198" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AM198">
         <v>8102026</v>
@@ -30102,19 +30095,19 @@
         <v>2109</v>
       </c>
       <c r="E199" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F199" t="s">
         <v>249</v>
       </c>
       <c r="G199" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H199" t="s">
         <v>145</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="J199">
         <v>4507469608</v>
@@ -30171,13 +30164,13 @@
         <v>20260812</v>
       </c>
       <c r="AJ199" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AK199">
         <v>20260812</v>
       </c>
       <c r="AL199" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AP199" t="s">
         <v>165</v>
@@ -30257,19 +30250,19 @@
         <v>2109</v>
       </c>
       <c r="E200" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F200" t="s">
         <v>249</v>
       </c>
       <c r="G200" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H200" t="s">
         <v>145</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="J200">
         <v>4507469608</v>
@@ -30326,7 +30319,7 @@
         <v>20260812</v>
       </c>
       <c r="AJ200" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AK200">
         <v>20260812</v>
@@ -30421,19 +30414,19 @@
         <v>2109</v>
       </c>
       <c r="E201" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F201" t="s">
         <v>249</v>
       </c>
       <c r="G201" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H201" t="s">
         <v>145</v>
       </c>
       <c r="I201" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="J201">
         <v>4507469608</v>
@@ -30490,7 +30483,7 @@
         <v>20260812</v>
       </c>
       <c r="AJ201" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AK201">
         <v>20260812</v>
@@ -30576,19 +30569,19 @@
         <v>2109</v>
       </c>
       <c r="E202" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F202" t="s">
         <v>249</v>
       </c>
       <c r="G202" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H202" t="s">
         <v>145</v>
       </c>
       <c r="I202" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="J202">
         <v>4507469608</v>
@@ -30639,7 +30632,7 @@
         <v>20260812</v>
       </c>
       <c r="AH202" s="1" t="s">
-        <v>443</v>
+        <v>595</v>
       </c>
       <c r="AI202">
         <v>20260812</v>
@@ -30731,19 +30724,19 @@
         <v>2109</v>
       </c>
       <c r="E203" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F203" t="s">
         <v>249</v>
       </c>
       <c r="G203" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H203" t="s">
         <v>145</v>
       </c>
       <c r="I203" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="J203">
         <v>4507488710</v>
@@ -30764,7 +30757,7 @@
         <v>2026</v>
       </c>
       <c r="T203" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V203" t="s">
         <v>205</v>
@@ -30776,7 +30769,7 @@
         <v>152</v>
       </c>
       <c r="Y203" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z203" t="s">
         <v>152</v>
@@ -30892,19 +30885,19 @@
         <v>2109</v>
       </c>
       <c r="E204" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F204" t="s">
         <v>249</v>
       </c>
       <c r="G204" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H204" t="s">
         <v>145</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="J204">
         <v>4507525630</v>
@@ -30925,7 +30918,7 @@
         <v>2026</v>
       </c>
       <c r="T204" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V204" t="s">
         <v>205</v>
@@ -30937,7 +30930,7 @@
         <v>152</v>
       </c>
       <c r="Y204" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z204" t="s">
         <v>152</v>
@@ -31053,19 +31046,19 @@
         <v>2109</v>
       </c>
       <c r="E205" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F205" t="s">
         <v>249</v>
       </c>
       <c r="G205" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H205" t="s">
         <v>145</v>
       </c>
       <c r="I205" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J205">
         <v>4507528292</v>
@@ -31086,7 +31079,7 @@
         <v>2026</v>
       </c>
       <c r="T205" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="V205" t="s">
         <v>205</v>
@@ -31098,7 +31091,7 @@
         <v>152</v>
       </c>
       <c r="Y205" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="Z205" t="s">
         <v>152</v>
@@ -31122,13 +31115,13 @@
         <v>20260815</v>
       </c>
       <c r="AJ205" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AK205">
         <v>20260815</v>
       </c>
       <c r="AL205" s="1" t="s">
-        <v>405</v>
+        <v>712</v>
       </c>
       <c r="AM205">
         <v>8</v>
